--- a/control/Control_Ejecucion.xlsx
+++ b/control/Control_Ejecucion.xlsx
@@ -1879,24 +1879,72 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38529 - Recuperacion de clave con CC</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REC-001</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SI</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTO</t>
+        </is>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperacion de clave: cambia la clave de un cliente registrado del listado</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38526 - OTP en la recuperacion de clave</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REC-OTP-001</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CC</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUTO</t>
+        </is>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTP en la recuperacion de clave (mismo escenario de 38529)</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
@@ -6753,7 +6801,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>Catalogo!$A$2:$A$12</xm:f>
+            <xm:f>Catalogo!$A$2:$A$14</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A500</xm:sqref>
         </x14:dataValidation>
@@ -7111,10 +7159,16 @@
       <c r="H11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="4"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatizado</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disponible en la hoja Control (REC-OTP-001). Mismo escenario de 38529; el evento del OTP no se ve en la app (verificacion fuera de la UI). En la app el OTP se pide despues de la clave nueva</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="210" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -7141,11 +7195,15 @@
       <c r="H12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>84</v>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatizado</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disponible en la hoja Control (REC-001). RN-R07 confirmada. En la app la clave nueva se pide antes del OTP</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:10" ht="255" x14ac:dyDescent="0.25">
@@ -7807,7 +7865,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8050,6 +8108,70 @@
         <v>242</v>
       </c>
     </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38529 - Recuperacion de clave con CC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38529</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperacion de clave</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@38529</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TipoDocumento (CC)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS). Clave = la nueva: vacia se genera segun RN-R07 y distinta de la actual; si se informa debe cumplir RN-R07. OTP: vacio = 000000. Cambia la clave del cliente: el listado guarda la nueva al confirmar; si falla tras enviar el cambio queda FALLIDO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38526 - OTP en la recuperacion de clave</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38526</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperacion de clave</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@38526</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TipoDocumento (CC)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mismo escenario y reglas de 38529 (el OTP es un paso del flujo de recuperacion). El evento "Recuperacion de contrasena" del OTP no se ve en la app: se verifica fuera de la UI.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/control/Control_Ejecucion.xlsx
+++ b/control/Control_Ejecucion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MiBanco\ATM_AppMovil_MiBanco\control\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GreenSQA\MiBanco\ATM-APP_MiBanco\ATM_AppMovil_MiBanco\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D22FD3B-F1B7-4B9A-8ADA-D444F3D803F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46CAC0F-64C8-435E-9141-33C09006CDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23265" windowHeight="9450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="314">
   <si>
     <t>Caso</t>
   </si>
@@ -195,9 +195,6 @@
     <t>Excluido</t>
   </si>
   <si>
-    <t>Requiere verificacion de SMS (pendiente por definir)</t>
-  </si>
-  <si>
     <t>38500</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
 3. La validación OTP es exitosa.
 4. La clave válida es aceptada.
 5. El registro finaliza correctamente y se muestra la confirmación.</t>
-  </si>
-  <si>
-    <t>Casos CE no se construyen por ahora</t>
   </si>
   <si>
     <t>38503</t>
@@ -291,9 +285,6 @@
 Verificar el teléfono asociado al usuario.</t>
   </si>
   <si>
-    <t>Casos CE no se construyen por ahora; ademas requiere SMS</t>
-  </si>
-  <si>
     <t>38504</t>
   </si>
   <si>
@@ -455,9 +446,6 @@
 2. Se muestra la confirmación de recuperación y el usuario es redirigido al Login.</t>
   </si>
   <si>
-    <t>RN-R07 confirmada</t>
-  </si>
-  <si>
     <t>38698</t>
   </si>
   <si>
@@ -820,12 +808,6 @@
     <t>CC o CE. Por ahora solo CC esta construido; una fila CE queda NO_EJECUTADA con su motivo.</t>
   </si>
   <si>
-    <t>Numero de documento (6 a 11 digitos). Escriba AUTO o deje vacio para que la automatizacion tome un cliente del listado datos/pool_clientes.xlsx.</t>
-  </si>
-  <si>
-    <t>Clave de 4 digitos. En el registro exitoso: vacia = se genera una valida segun RN-R07; si se informa debe cumplir RN-R07. En casos futuros (claves erradas) se usara tal como se escriba.</t>
-  </si>
-  <si>
     <t>Codigo OTP de 6 digitos. Vacio = 000000 (OTP fijo del ambiente de pruebas).</t>
   </si>
   <si>
@@ -883,9 +865,6 @@
     <t>7. Resultados posibles</t>
   </si>
   <si>
-    <t>EXITOSA; FALLIDA (ver Detalle y evidencias); CANCELADA (indisponibilidad del sistema, ver seccion 9); PENDIENTE (no se ejecuto porque el proceso se detuvo por indisponibilidad); NO_EJECUTADA (rechazada por el motor de reglas o sin escenario); OMITIDA (Ejecutar = NO).</t>
-  </si>
-  <si>
     <t>8. Hoja Casos de Prueba</t>
   </si>
   <si>
@@ -895,15 +874,9 @@
     <t>9. Indisponibilidad del sistema</t>
   </si>
   <si>
-    <t>Si en cualquier momento de un flujo la app muestra "Validacion fallida. No es posible atender tu solicitud por este canal...", la automatizacion guarda la evidencia y cancela la iteracion: no continua el flujo (evita falsos positivos) y la deja CANCELADA, no FALLIDA. Si el cliente venia del listado, vuelve a DISPONIBLE.</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Detencion del proceso</t>
   </si>
   <si>
-    <t>Si esto ocurre en 2 iteraciones de la misma ejecucion, se detiene todo: las filas restantes quedan PENDIENTE, se genera el reporte y el control de resultados, y en la carpeta de la ejecucion queda el archivo NOVEDAD_INDISPONIBILIDAD.txt. Vuelva a ejecutar en otra oportunidad.</t>
-  </si>
-  <si>
     <t>IdAzure</t>
   </si>
   <si>
@@ -928,214 +901,400 @@
     <t>NO</t>
   </si>
   <si>
-    <t xml:space="preserve">38499 - SMS por registro exitoso con CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como 38498, pero AUTO toma un cliente DISPONIBLE con LINEA_SMS = SI. Ejecutar en el dispositivo fisico con la SIM de esa linea. Espera el SMS de registro (texto provisional en sms.patron.registro).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38519 - Login exitoso con CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume. Con documento informado, Clave vacia = la del listado; si se informa, 4 digitos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS_INGRESO - SMS por ingreso exitoso con CC (sin caso Azure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS_INGRESO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@SMS_INGRESO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como 38519, pero AUTO toma un cliente REGISTRADO con LINEA_SMS = SI. Ejecutar en el dispositivo fisico con la SIM de esa linea. Espera el SMS 'ingreso exitoso en el canal App'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login con cliente registrado del listado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS-ING-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requiere el dispositivo fisico con la SIM de la linea de prueba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REG-SMS-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente: clientes con la linea de prueba sin registrar (solicitados)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control. Requiere dispositivo fisico con la SIM de la linea de prueba y clientes con esa linea sin registrar; texto del SMS provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numero de documento (6 a 11 digitos). AUTO o vacio: en registro toma un cliente DISPONIBLE del listado datos/pool_clientes.xlsx; en login toma un cliente REGISTRADO con su clave (no lo consume). Los casos de SMS solo toman clientes con LINEA_SMS = SI y los demas casos nunca los toman.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clave de 4 digitos. Registro exitoso: vacia = se genera una valida segun RN-R07; si se informa debe cumplir RN-R07. Login: vacia = la clave guardada en el listado; con AUTO debe ir vacia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38503 - SMS por registro exitoso con CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TipoDocumento (CE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variante CE de 38499 (mismo escenario). AUTO toma un CE DISPONIBLE con LINEA_SMS = SI. Ejecutar en el dispositivo fisico con la SIM de esa linea. Clientes escasos: un solo intento por cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REG-SMS-CE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registro CE con la linea de prueba: un solo intento (clientes escasos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control. Mismo escenario de 38499 con CE; requiere el dispositivo fisico con la SIM de la linea de prueba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXITOSA; FALLIDA (ver Detalle y evidencias; incluye la indisponibilidad del sistema que persiste tras los reintentos, ver seccion 9); PENDIENTE (no se ejecuto porque el proceso se detuvo por indisponibilidad); NO_EJECUTADA (rechazada por el motor de reglas o sin escenario); OMITIDA (Ejecutar = NO).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si al ejecutar una accion la app muestra "Validacion fallida. No es posible atender tu solicitud por este canal...", la automatizacion acepta el aviso (Entiendo) y repite la accion que lo provoco, hasta 2 veces (indisponibilidad.reintentos). Si persiste, guarda la evidencia y la iteracion queda FALLIDA por indisponibilidad. Si el cliente venia del listado, vuelve a DISPONIBLE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si 2 iteraciones de la misma ejecucion fallan por indisponibilidad, se detiene todo: las filas restantes quedan PENDIENTE, se genera el reporte y el control de resultados, y en la carpeta de la ejecucion queda el archivo NOVEDAD_INDISPONIBILIDAD.txt. Vuelva a ejecutar en otra oportunidad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38700 - Ultimo ingreso en el encabezado del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como 38519: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume. Si es el primer ingreso del cliente, cierra sesion y vuelve a ingresar para que aparezca 'Ultimo ingreso'. Cierra sesion al terminar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultimo ingreso en el encabezado del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cubierto por el escenario de 38700 (consolidacion de casos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (HOME-001). Formato de ultimo ingreso aceptado: DD/MM/AAAA - HH:MM:SS. El nombre del saludo no se valida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38520 - Login exitoso con CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variante CE de 38519 (mismo escenario). AUTO o vacio toma un CE REGISTRADO con clave del listado (prefiere los que no tienen LINEA_SMS); no lo consume. Cierra sesion al terminar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOG-CE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Login con CE registrado del listado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (LOG-CE-001). Mismo escenario de 38519 con CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38502 - Registro exitoso con CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variante CE de 38498 (mismo escenario). AUTO toma un CE DISPONIBLE sin LINEA_SMS (los de la linea se reservan para 38503). Hoy no hay CE disponibles sin linea: solicitar datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REG-CE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente: no hay clientes CE disponibles sin la linea de prueba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (REG-CE-001). Mismo escenario de 38498 con CE; sin ejecutar por falta de datos CE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38699 - Saludo y pregunta del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTO o vacio toma un cliente REGISTRADO con clave del listado; no lo consume. Cierra sesion al terminar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saludo y pregunta del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (HOME-002). El nombre del saludo no se valida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38703 - Acceso Bre-B en la parte superior del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME-ACC-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceso Bre-B (parte superior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (HOME-ACC-001). La identidad visual (paso 5) queda manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38704 - Acceso Pedir Credito en la parte superior del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME-ACC-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceso Pedir Credito (parte superior)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (HOME-ACC-002). La identidad visual (paso 5) queda manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38711 - Menu inferior del Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@38711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME-MENU-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menu inferior: 5 accesos en orden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponible en la hoja Control (HOME-MENU-001). El estado activo de Inicio queda manual (no se expone a la automatizacion)</t>
+    <t>38499 - SMS por registro exitoso con CC</t>
+  </si>
+  <si>
+    <t>@38499</t>
+  </si>
+  <si>
+    <t>Como 38498, pero AUTO toma un cliente DISPONIBLE con LINEA_SMS = SI. Ejecutar en el dispositivo fisico con la SIM de esa linea. Espera el SMS de registro (texto provisional en sms.patron.registro).</t>
+  </si>
+  <si>
+    <t>38519 - Login exitoso con CC</t>
+  </si>
+  <si>
+    <t>@38519</t>
+  </si>
+  <si>
+    <t>NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume. Con documento informado, Clave vacia = la del listado; si se informa, 4 digitos.</t>
+  </si>
+  <si>
+    <t>LOG-001</t>
+  </si>
+  <si>
+    <t>Login con cliente registrado del listado</t>
+  </si>
+  <si>
+    <t>REG-SMS-001</t>
+  </si>
+  <si>
+    <t>Pendiente: clientes con la linea de prueba sin registrar (solicitados)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Requiere dispositivo fisico con la SIM de la linea de prueba y clientes con esa linea sin registrar; texto del SMS provisional</t>
+  </si>
+  <si>
+    <t>Numero de documento (6 a 11 digitos). AUTO o vacio: en registro toma un cliente DISPONIBLE del listado datos/pool_clientes.xlsx; en login toma un cliente REGISTRADO con su clave (no lo consume). Los casos de SMS solo toman clientes con LINEA_SMS = SI y los demas casos nunca los toman.</t>
+  </si>
+  <si>
+    <t>Clave de 4 digitos. Registro exitoso: vacia = se genera una valida segun RN-R07; si se informa debe cumplir RN-R07. Login: vacia = la clave guardada en el listado; con AUTO debe ir vacia.</t>
+  </si>
+  <si>
+    <t>38503 - SMS por registro exitoso con CE</t>
+  </si>
+  <si>
+    <t>@38503</t>
+  </si>
+  <si>
+    <t>TipoDocumento (CE)</t>
+  </si>
+  <si>
+    <t>Variante CE de 38499 (mismo escenario). AUTO toma un CE DISPONIBLE con LINEA_SMS = SI. Ejecutar en el dispositivo fisico con la SIM de esa linea. Clientes escasos: un solo intento por cliente.</t>
+  </si>
+  <si>
+    <t>REG-SMS-CE-001</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>Registro CE con la linea de prueba: un solo intento (clientes escasos)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Mismo escenario de 38499 con CE; requiere el dispositivo fisico con la SIM de la linea de prueba</t>
+  </si>
+  <si>
+    <t>EXITOSA; FALLIDA (ver Detalle y evidencias; incluye la indisponibilidad del sistema que persiste tras los reintentos, ver seccion 9); PENDIENTE (no se ejecuto porque el proceso se detuvo por indisponibilidad); NO_EJECUTADA (rechazada por el motor de reglas o sin escenario); OMITIDA (Ejecutar = NO).</t>
+  </si>
+  <si>
+    <t>Si al ejecutar una accion la app muestra "Validacion fallida. No es posible atender tu solicitud por este canal...", la automatizacion acepta el aviso (Entiendo) y repite la accion que lo provoco, hasta 2 veces (indisponibilidad.reintentos). Si persiste, guarda la evidencia y la iteracion queda FALLIDA por indisponibilidad. Si el cliente venia del listado, vuelve a DISPONIBLE.</t>
+  </si>
+  <si>
+    <t>Si 2 iteraciones de la misma ejecucion fallan por indisponibilidad, se detiene todo: las filas restantes quedan PENDIENTE, se genera el reporte y el control de resultados, y en la carpeta de la ejecucion queda el archivo NOVEDAD_INDISPONIBILIDAD.txt. Vuelva a ejecutar en otra oportunidad.</t>
+  </si>
+  <si>
+    <t>38700 - Ultimo ingreso en el encabezado del Home</t>
+  </si>
+  <si>
+    <t>@38700</t>
+  </si>
+  <si>
+    <t>Como 38519: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume. Si es el primer ingreso del cliente, cierra sesion y vuelve a ingresar para que aparezca 'Ultimo ingreso'. Cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>HOME-001</t>
+  </si>
+  <si>
+    <t>Ultimo ingreso en el encabezado del Home</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (HOME-001). Formato de ultimo ingreso aceptado: DD/MM/AAAA - HH:MM:SS. El nombre del saludo no se valida</t>
+  </si>
+  <si>
+    <t>38520 - Login exitoso con CE</t>
+  </si>
+  <si>
+    <t>@38520</t>
+  </si>
+  <si>
+    <t>Variante CE de 38519 (mismo escenario). AUTO o vacio toma un CE REGISTRADO con clave del listado (prefiere los que no tienen LINEA_SMS); no lo consume. Cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>LOG-CE-001</t>
+  </si>
+  <si>
+    <t>Login con CE registrado del listado</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (LOG-CE-001). Mismo escenario de 38519 con CE</t>
+  </si>
+  <si>
+    <t>38502 - Registro exitoso con CE</t>
+  </si>
+  <si>
+    <t>@38502</t>
+  </si>
+  <si>
+    <t>Variante CE de 38498 (mismo escenario). AUTO toma un CE DISPONIBLE sin LINEA_SMS (los de la linea se reservan para 38503). Hoy no hay CE disponibles sin linea: solicitar datos.</t>
+  </si>
+  <si>
+    <t>REG-CE-001</t>
+  </si>
+  <si>
+    <t>Pendiente: no hay clientes CE disponibles sin la linea de prueba</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (REG-CE-001). Mismo escenario de 38498 con CE; sin ejecutar por falta de datos CE</t>
+  </si>
+  <si>
+    <t>38699 - Saludo y pregunta del Home</t>
+  </si>
+  <si>
+    <t>@38699</t>
+  </si>
+  <si>
+    <t>AUTO o vacio toma un cliente REGISTRADO con clave del listado; no lo consume. Cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>HOME-002</t>
+  </si>
+  <si>
+    <t>Saludo y pregunta del Home</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (HOME-002). El nombre del saludo no se valida</t>
+  </si>
+  <si>
+    <t>38703 - Acceso Bre-B en la parte superior del Home</t>
+  </si>
+  <si>
+    <t>@38703</t>
+  </si>
+  <si>
+    <t>HOME-ACC-001</t>
+  </si>
+  <si>
+    <t>Acceso Bre-B (parte superior)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (HOME-ACC-001). La identidad visual (paso 5) queda manual</t>
+  </si>
+  <si>
+    <t>38704 - Acceso Pedir Credito en la parte superior del Home</t>
+  </si>
+  <si>
+    <t>@38704</t>
+  </si>
+  <si>
+    <t>HOME-ACC-002</t>
+  </si>
+  <si>
+    <t>Acceso Pedir Credito (parte superior)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (HOME-ACC-002). La identidad visual (paso 5) queda manual</t>
+  </si>
+  <si>
+    <t>38711 - Menu inferior del Home</t>
+  </si>
+  <si>
+    <t>@38711</t>
+  </si>
+  <si>
+    <t>HOME-MENU-001</t>
+  </si>
+  <si>
+    <t>Menu inferior: 5 accesos en orden</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (HOME-MENU-001). El estado activo de Inicio queda manual (no se expone a la automatizacion)</t>
+  </si>
+  <si>
+    <t>38529 - Recuperacion de clave con CC</t>
+  </si>
+  <si>
+    <t>REC-001</t>
+  </si>
+  <si>
+    <t>Recuperacion de clave: cambia la clave de un cliente registrado del listado</t>
+  </si>
+  <si>
+    <t>38526 - OTP en la recuperacion de clave</t>
+  </si>
+  <si>
+    <t>REC-OTP-001</t>
+  </si>
+  <si>
+    <t>OTP en la recuperacion de clave (mismo escenario de 38529)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (REC-OTP-001). Mismo escenario de 38529; el evento del OTP no se ve en la app (verificacion fuera de la UI). En la app el OTP se pide despues de la clave nueva</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (REC-001). RN-R07 confirmada. En la app la clave nueva se pide antes del OTP</t>
+  </si>
+  <si>
+    <t>@38529</t>
+  </si>
+  <si>
+    <t>NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS). Clave = la nueva: vacia se genera segun RN-R07 y distinta de la actual; si se informa debe cumplir RN-R07. OTP: vacio = 000000. Cambia la clave del cliente: el listado guarda la nueva al confirmar; si falla tras enviar el cambio queda FALLIDO.</t>
+  </si>
+  <si>
+    <t>@38526</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38529 (el OTP es un paso del flujo de recuperacion). El evento "Recuperacion de contrasena" del OTP no se ve en la app: se verifica fuera de la UI.</t>
+  </si>
+  <si>
+    <t>TipoProducto</t>
+  </si>
+  <si>
+    <t>Monto</t>
+  </si>
+  <si>
+    <t>AHORRO</t>
+  </si>
+  <si>
+    <t>CORRIENTE</t>
+  </si>
+  <si>
+    <t>PRESTAMO</t>
+  </si>
+  <si>
+    <t>ROTATIVO</t>
+  </si>
+  <si>
+    <t>PRE_APROBADO</t>
+  </si>
+  <si>
+    <t>38702 - Credito pre-aprobado en el Home</t>
+  </si>
+  <si>
+    <t>@38702</t>
+  </si>
+  <si>
+    <t>Como 38519: AUTO toma un cliente REGISTRADO con clave que muestre el banner de pre-aprobado (columna PRODUCTOS_HOME del listado), revisando hasta 3 clientes. TipoProducto vacio o PRE_APROBADO. El banner no muestra saldo (control de cambios #8): si se informa Monto, la fila falla mostrando esa diferencia. Cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>38705 - Producto cuenta de ahorro en el Home</t>
+  </si>
+  <si>
+    <t>@38705</t>
+  </si>
+  <si>
+    <t>Como 38702 con AHORRO. Valida el titulo Cuentas de ahorro **** 1234, la etiqueta, el saldo con formato $22.746.864,51 y el icono de ocultar montos. Monto opcional: si se informa, se compara con el saldo.</t>
+  </si>
+  <si>
+    <t>38706 - Producto cuenta corriente en el Home</t>
+  </si>
+  <si>
+    <t>@38706</t>
+  </si>
+  <si>
+    <t>Como 38705 con CORRIENTE. Hoy ningun cliente revisado tiene cuenta corriente: solicitar datos o informar el documento.</t>
+  </si>
+  <si>
+    <t>38707 - Producto credito de libre inversion (Prestamos) en el Home</t>
+  </si>
+  <si>
+    <t>@38707</t>
+  </si>
+  <si>
+    <t>Como 38702 con PRESTAMO (la app muestra estos creditos como Prestamos). Valida titulo, saldo con formato, estado de la cuota (Cuota vencio 1 Jun) y que la tarjeta se pueda abrir. Monto opcional.</t>
+  </si>
+  <si>
+    <t>38708 - Producto credito rotativo en el Home</t>
+  </si>
+  <si>
+    <t>@38708</t>
+  </si>
+  <si>
+    <t>Como 38702 con ROTATIVO. Valida Credito Rotativo con la etiqueta Cupo aprobado, el monto con formato y que la tarjeta se pueda abrir. Monto opcional.</t>
+  </si>
+  <si>
+    <t>38709 - Saldos de los productos en el Home</t>
+  </si>
+  <si>
+    <t>@38709</t>
+  </si>
+  <si>
+    <t>TipoDocumento (CC), TipoProducto, Monto</t>
+  </si>
+  <si>
+    <t>Compara el Monto (saldo esperado segun el backend, p. ej. 22746864.51) con el de las tarjetas del TipoProducto indicado y valida la tarjeta como en su caso. Una fila por producto a comparar. Monto y TipoProducto son obligatorios.</t>
+  </si>
+  <si>
+    <t>PROD-AHO-001</t>
+  </si>
+  <si>
+    <t>Cuenta de ahorro en el Home</t>
+  </si>
+  <si>
+    <t>PROD-PRE-001</t>
+  </si>
+  <si>
+    <t>Prestamos (libre inversion) en el Home</t>
+  </si>
+  <si>
+    <t>PROD-ROT-001</t>
+  </si>
+  <si>
+    <t>Credito rotativo en el Home</t>
+  </si>
+  <si>
+    <t>PROD-PRA-001</t>
+  </si>
+  <si>
+    <t>Banner de credito pre-aprobado</t>
+  </si>
+  <si>
+    <t>PROD-COR-001</t>
+  </si>
+  <si>
+    <t>SALDO-001</t>
+  </si>
+  <si>
+    <t>Solo casos de productos del Home (38702, 38705 a 38709). Lista: AHORRO, CORRIENTE, PRESTAMO (en la app se llama Prestamos; el caso 38707 lo llama libre inversion), ROTATIVO, PRE_APROBADO. Vacio = el producto del caso; en 38709 es obligatorio (producto cuyo saldo se compara). Con NumDocumento AUTO se busca en el listado un cliente REGISTRADO que muestre el producto (columna PRODUCTOS_HOME), revisando hasta 3 clientes. Dejar vacia en los demas casos.</t>
+  </si>
+  <si>
+    <t>Solo casos de productos del Home. Saldo esperado del producto segun el backend, como numero (ej. 22746864.51). Vacio = solo se valida el formato del monto en la app ($22.746.864,51). Obligatorio en 38709. Dejar vacia en los demas casos.</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (PROD-PRA-001). Escenario de productos del Home (38705)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (PROD-AHO-001). Escenario de productos del Home (38705)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (PROD-COR-001 (pendiente de datos)). Escenario de productos del Home (38705)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (PROD-PRE-001). Escenario de productos del Home (38705)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (PROD-ROT-001). Escenario de productos del Home (38705)</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (SALDO-001 (pendiente del monto esperado)). Escenario de productos del Home (38705)</t>
+  </si>
+  <si>
+    <t>38698 - Skeleton de carga del Home</t>
+  </si>
+  <si>
+    <t>@38698</t>
+  </si>
+  <si>
+    <t>Como 38519: AUTO toma un cliente REGISTRADO con clave. Al ingresar valida que Tus cuentas y Tus creditos muestren el indicador de carga (Cargando..., skeleton) antes de los saldos y que luego aparezcan los montos. Captura del skeleton como evidencia. Si el backend responde muy rapido el skeleton puede no alcanzar a verse y la fila falla con ese detalle. Cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>SKEL-001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>43110437.46</t>
+  </si>
+  <si>
+    <t>SALDO-002</t>
+  </si>
+  <si>
+    <t>43110438.46</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (SKEL-001)</t>
+  </si>
+  <si>
+    <t>Pendiente: ningun cliente registrado muestra cuenta corriente (verificado 12/10); informar un documento con el producto</t>
+  </si>
+  <si>
+    <t>Verificado 12/10 con monto tomado de la app (no del backend). Pendiente: Monto esperado segun el backend</t>
+  </si>
+  <si>
+    <t>Verificacion tecnica 12/10: monto alterado en 1 peso falla como se espera. Eliminar o reutilizar con montos del backend</t>
+  </si>
+  <si>
+    <t>Skeleton (Cargando...) mientras el Home obtiene los saldos; se observa por DevTools del WebView</t>
   </si>
 </sst>
 </file>
@@ -1554,8 +1713,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J500"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1563,10 +1722,11 @@
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="8" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1589,10 +1749,16 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1600,7 +1766,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -1610,11 +1776,13 @@
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1622,7 +1790,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
@@ -1632,11 +1800,13 @@
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1644,7 +1814,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -1654,16 +1824,18 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -1676,41 +1848,45 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -1720,38 +1896,42 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -1764,38 +1944,42 @@
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
@@ -1808,16 +1992,18 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -1830,16 +2016,18 @@
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -1852,16 +2040,18 @@
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
@@ -1874,159 +2064,277 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38529 - Recuperacion de clave con CC</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REC-001</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SI</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CC</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUTO</t>
-        </is>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recuperacion de clave: cambia la clave de un cliente registrado del listado</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38526 - OTP en la recuperacion de clave</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REC-OTP-001</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SI</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CC</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUTO</t>
-        </is>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTP en la recuperacion de clave (mismo escenario de 38529)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H24" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2035,8 +2343,10 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2045,8 +2355,10 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2055,8 +2367,10 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2065,8 +2379,10 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2075,8 +2391,10 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2085,8 +2403,10 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2095,8 +2415,10 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2105,8 +2427,10 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2115,8 +2439,10 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2125,8 +2451,10 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2135,8 +2463,10 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2145,8 +2475,10 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2155,8 +2487,10 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2165,8 +2499,10 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2175,8 +2511,10 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2185,8 +2523,10 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2195,8 +2535,10 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2205,8 +2547,10 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2215,8 +2559,10 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2225,8 +2571,10 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2235,8 +2583,10 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2245,8 +2595,10 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2255,8 +2607,10 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2265,8 +2619,10 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2275,8 +2631,10 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2285,8 +2643,10 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2295,8 +2655,10 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2305,8 +2667,10 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2315,8 +2679,10 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2325,8 +2691,10 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2335,8 +2703,10 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2345,8 +2715,10 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2355,8 +2727,10 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2365,8 +2739,10 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2375,8 +2751,10 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2385,8 +2763,10 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2395,8 +2775,10 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2405,8 +2787,10 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2415,8 +2799,10 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2425,8 +2811,10 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2435,8 +2823,10 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2445,8 +2835,10 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2455,8 +2847,10 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2465,8 +2859,10 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2475,8 +2871,10 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -2485,8 +2883,10 @@
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2495,8 +2895,10 @@
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -2505,8 +2907,10 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -2515,8 +2919,10 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -2525,8 +2931,10 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2535,8 +2943,10 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -2545,8 +2955,10 @@
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -2555,8 +2967,10 @@
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -2565,8 +2979,10 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -2575,8 +2991,10 @@
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2585,8 +3003,10 @@
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -2595,8 +3015,10 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -2605,8 +3027,10 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -2615,8 +3039,10 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -2625,8 +3051,10 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2635,8 +3063,10 @@
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -2645,8 +3075,10 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -2655,8 +3087,10 @@
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2665,8 +3099,10 @@
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -2675,8 +3111,10 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -2685,8 +3123,10 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -2695,8 +3135,10 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -2705,8 +3147,10 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -2715,8 +3159,10 @@
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -2725,8 +3171,10 @@
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -2735,8 +3183,10 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -2745,8 +3195,10 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -2755,8 +3207,10 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -2765,8 +3219,10 @@
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -2775,8 +3231,10 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -2785,8 +3243,10 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -2795,8 +3255,10 @@
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -2805,8 +3267,10 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -2815,8 +3279,10 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -2825,8 +3291,10 @@
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -2835,8 +3303,10 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -2845,8 +3315,10 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106" s="2"/>
+      <c r="J106" s="2"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -2855,8 +3327,10 @@
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -2865,8 +3339,10 @@
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -2875,8 +3351,10 @@
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I109" s="2"/>
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -2885,8 +3363,10 @@
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -2895,8 +3375,10 @@
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -2905,8 +3387,10 @@
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -2915,8 +3399,10 @@
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -2925,8 +3411,10 @@
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -2935,8 +3423,10 @@
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -2945,8 +3435,10 @@
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -2955,8 +3447,10 @@
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -2965,8 +3459,10 @@
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -2975,8 +3471,10 @@
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -2985,8 +3483,10 @@
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -2995,8 +3495,10 @@
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -3005,8 +3507,10 @@
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -3015,8 +3519,10 @@
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -3025,8 +3531,10 @@
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -3035,8 +3543,10 @@
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -3045,8 +3555,10 @@
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126" s="2"/>
+      <c r="J126" s="2"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -3055,8 +3567,10 @@
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -3065,8 +3579,10 @@
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -3075,8 +3591,10 @@
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -3085,8 +3603,10 @@
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -3095,8 +3615,10 @@
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -3105,8 +3627,10 @@
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -3115,8 +3639,10 @@
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -3125,8 +3651,10 @@
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -3135,8 +3663,10 @@
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -3145,8 +3675,10 @@
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -3155,8 +3687,10 @@
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -3165,8 +3699,10 @@
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -3175,8 +3711,10 @@
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -3185,8 +3723,10 @@
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -3195,8 +3735,10 @@
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -3205,8 +3747,10 @@
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -3215,8 +3759,10 @@
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -3225,8 +3771,10 @@
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -3235,8 +3783,10 @@
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I145" s="2"/>
+      <c r="J145" s="2"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -3245,8 +3795,10 @@
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -3255,8 +3807,10 @@
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I147" s="2"/>
+      <c r="J147" s="2"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -3265,8 +3819,10 @@
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I148" s="2"/>
+      <c r="J148" s="2"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -3275,8 +3831,10 @@
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -3285,8 +3843,10 @@
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -3295,8 +3855,10 @@
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I151" s="2"/>
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -3305,8 +3867,10 @@
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I152" s="2"/>
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -3315,8 +3879,10 @@
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I153" s="2"/>
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -3325,8 +3891,10 @@
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I154" s="2"/>
+      <c r="J154" s="2"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -3335,8 +3903,10 @@
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I155" s="2"/>
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -3345,8 +3915,10 @@
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -3355,8 +3927,10 @@
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -3365,8 +3939,10 @@
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -3375,8 +3951,10 @@
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I159" s="2"/>
+      <c r="J159" s="2"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -3385,8 +3963,10 @@
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I160" s="2"/>
+      <c r="J160" s="2"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -3395,8 +3975,10 @@
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -3405,8 +3987,10 @@
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -3415,8 +3999,10 @@
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -3425,8 +4011,10 @@
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I164" s="2"/>
+      <c r="J164" s="2"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -3435,8 +4023,10 @@
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I165" s="2"/>
+      <c r="J165" s="2"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -3445,8 +4035,10 @@
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -3455,8 +4047,10 @@
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I167" s="2"/>
+      <c r="J167" s="2"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -3465,8 +4059,10 @@
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I168" s="2"/>
+      <c r="J168" s="2"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -3475,8 +4071,10 @@
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I169" s="2"/>
+      <c r="J169" s="2"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -3485,8 +4083,10 @@
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -3495,8 +4095,10 @@
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I171" s="2"/>
+      <c r="J171" s="2"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -3505,8 +4107,10 @@
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I172" s="2"/>
+      <c r="J172" s="2"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -3515,8 +4119,10 @@
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -3525,8 +4131,10 @@
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -3535,8 +4143,10 @@
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I175" s="2"/>
+      <c r="J175" s="2"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -3545,8 +4155,10 @@
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I176" s="2"/>
+      <c r="J176" s="2"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -3555,8 +4167,10 @@
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -3565,8 +4179,10 @@
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -3575,8 +4191,10 @@
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I179" s="2"/>
+      <c r="J179" s="2"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -3585,8 +4203,10 @@
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -3595,8 +4215,10 @@
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -3605,8 +4227,10 @@
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -3615,8 +4239,10 @@
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -3625,8 +4251,10 @@
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I184" s="2"/>
+      <c r="J184" s="2"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -3635,8 +4263,10 @@
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I185" s="2"/>
+      <c r="J185" s="2"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -3645,8 +4275,10 @@
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I186" s="2"/>
+      <c r="J186" s="2"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -3655,8 +4287,10 @@
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I187" s="2"/>
+      <c r="J187" s="2"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -3665,8 +4299,10 @@
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I188" s="2"/>
+      <c r="J188" s="2"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -3675,8 +4311,10 @@
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I189" s="2"/>
+      <c r="J189" s="2"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -3685,8 +4323,10 @@
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I190" s="2"/>
+      <c r="J190" s="2"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -3695,8 +4335,10 @@
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I191" s="2"/>
+      <c r="J191" s="2"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -3705,8 +4347,10 @@
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -3715,8 +4359,10 @@
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I193" s="2"/>
+      <c r="J193" s="2"/>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -3725,8 +4371,10 @@
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -3735,8 +4383,10 @@
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I195" s="2"/>
+      <c r="J195" s="2"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -3745,8 +4395,10 @@
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -3755,8 +4407,10 @@
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -3765,8 +4419,10 @@
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I198" s="2"/>
+      <c r="J198" s="2"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -3775,8 +4431,10 @@
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I199" s="2"/>
+      <c r="J199" s="2"/>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -3785,8 +4443,10 @@
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -3795,8 +4455,10 @@
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I201" s="2"/>
+      <c r="J201" s="2"/>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -3805,8 +4467,10 @@
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I202" s="2"/>
+      <c r="J202" s="2"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -3815,8 +4479,10 @@
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I203" s="2"/>
+      <c r="J203" s="2"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -3825,8 +4491,10 @@
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I204" s="2"/>
+      <c r="J204" s="2"/>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -3835,8 +4503,10 @@
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I205" s="2"/>
+      <c r="J205" s="2"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -3845,8 +4515,10 @@
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I206" s="2"/>
+      <c r="J206" s="2"/>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -3855,8 +4527,10 @@
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I207" s="2"/>
+      <c r="J207" s="2"/>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -3865,8 +4539,10 @@
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I208" s="2"/>
+      <c r="J208" s="2"/>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -3875,8 +4551,10 @@
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I209" s="2"/>
+      <c r="J209" s="2"/>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -3885,8 +4563,10 @@
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I210" s="2"/>
+      <c r="J210" s="2"/>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -3895,8 +4575,10 @@
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I211" s="2"/>
+      <c r="J211" s="2"/>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -3905,8 +4587,10 @@
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -3915,8 +4599,10 @@
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -3925,8 +4611,10 @@
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I214" s="2"/>
+      <c r="J214" s="2"/>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -3935,8 +4623,10 @@
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -3945,8 +4635,10 @@
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -3955,8 +4647,10 @@
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -3965,8 +4659,10 @@
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -3975,8 +4671,10 @@
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -3985,8 +4683,10 @@
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -3995,8 +4695,10 @@
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -4005,8 +4707,10 @@
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -4015,8 +4719,10 @@
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -4025,8 +4731,10 @@
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I224" s="2"/>
+      <c r="J224" s="2"/>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -4035,8 +4743,10 @@
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I225" s="2"/>
+      <c r="J225" s="2"/>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -4045,8 +4755,10 @@
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I226" s="2"/>
+      <c r="J226" s="2"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -4055,8 +4767,10 @@
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I227" s="2"/>
+      <c r="J227" s="2"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -4065,8 +4779,10 @@
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I228" s="2"/>
+      <c r="J228" s="2"/>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -4075,8 +4791,10 @@
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I229" s="2"/>
+      <c r="J229" s="2"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -4085,8 +4803,10 @@
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I230" s="2"/>
+      <c r="J230" s="2"/>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -4095,8 +4815,10 @@
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I231" s="2"/>
+      <c r="J231" s="2"/>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -4105,8 +4827,10 @@
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I232" s="2"/>
+      <c r="J232" s="2"/>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -4115,8 +4839,10 @@
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I233" s="2"/>
+      <c r="J233" s="2"/>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -4125,8 +4851,10 @@
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I234" s="2"/>
+      <c r="J234" s="2"/>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -4135,8 +4863,10 @@
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I235" s="2"/>
+      <c r="J235" s="2"/>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -4145,8 +4875,10 @@
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I236" s="2"/>
+      <c r="J236" s="2"/>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -4155,8 +4887,10 @@
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I237" s="2"/>
+      <c r="J237" s="2"/>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -4165,8 +4899,10 @@
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I238" s="2"/>
+      <c r="J238" s="2"/>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -4175,8 +4911,10 @@
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I239" s="2"/>
+      <c r="J239" s="2"/>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -4185,8 +4923,10 @@
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I240" s="2"/>
+      <c r="J240" s="2"/>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -4195,8 +4935,10 @@
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I241" s="2"/>
+      <c r="J241" s="2"/>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -4205,8 +4947,10 @@
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I242" s="2"/>
+      <c r="J242" s="2"/>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -4215,8 +4959,10 @@
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I243" s="2"/>
+      <c r="J243" s="2"/>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -4225,8 +4971,10 @@
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I244" s="2"/>
+      <c r="J244" s="2"/>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -4235,8 +4983,10 @@
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I245" s="2"/>
+      <c r="J245" s="2"/>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -4245,8 +4995,10 @@
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I246" s="2"/>
+      <c r="J246" s="2"/>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -4255,8 +5007,10 @@
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I247" s="2"/>
+      <c r="J247" s="2"/>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -4265,8 +5019,10 @@
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I248" s="2"/>
+      <c r="J248" s="2"/>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -4275,8 +5031,10 @@
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I249" s="2"/>
+      <c r="J249" s="2"/>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -4285,8 +5043,10 @@
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I250" s="2"/>
+      <c r="J250" s="2"/>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -4295,8 +5055,10 @@
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I251" s="2"/>
+      <c r="J251" s="2"/>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -4305,8 +5067,10 @@
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I252" s="2"/>
+      <c r="J252" s="2"/>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -4315,8 +5079,10 @@
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I253" s="2"/>
+      <c r="J253" s="2"/>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -4325,8 +5091,10 @@
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I254" s="2"/>
+      <c r="J254" s="2"/>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -4335,8 +5103,10 @@
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I255" s="2"/>
+      <c r="J255" s="2"/>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -4345,8 +5115,10 @@
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I256" s="2"/>
+      <c r="J256" s="2"/>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -4355,8 +5127,10 @@
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I257" s="2"/>
+      <c r="J257" s="2"/>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -4365,8 +5139,10 @@
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I258" s="2"/>
+      <c r="J258" s="2"/>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -4375,8 +5151,10 @@
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I259" s="2"/>
+      <c r="J259" s="2"/>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -4385,8 +5163,10 @@
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I260" s="2"/>
+      <c r="J260" s="2"/>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -4395,8 +5175,10 @@
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I261" s="2"/>
+      <c r="J261" s="2"/>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -4405,8 +5187,10 @@
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I262" s="2"/>
+      <c r="J262" s="2"/>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -4415,8 +5199,10 @@
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I263" s="2"/>
+      <c r="J263" s="2"/>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -4425,8 +5211,10 @@
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I264" s="2"/>
+      <c r="J264" s="2"/>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -4435,8 +5223,10 @@
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I265" s="2"/>
+      <c r="J265" s="2"/>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -4445,8 +5235,10 @@
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I266" s="2"/>
+      <c r="J266" s="2"/>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -4455,8 +5247,10 @@
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I267" s="2"/>
+      <c r="J267" s="2"/>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -4465,8 +5259,10 @@
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I268" s="2"/>
+      <c r="J268" s="2"/>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -4475,8 +5271,10 @@
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I269" s="2"/>
+      <c r="J269" s="2"/>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -4485,8 +5283,10 @@
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I270" s="2"/>
+      <c r="J270" s="2"/>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -4495,8 +5295,10 @@
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I271" s="2"/>
+      <c r="J271" s="2"/>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -4505,8 +5307,10 @@
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I272" s="2"/>
+      <c r="J272" s="2"/>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -4515,8 +5319,10 @@
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I273" s="2"/>
+      <c r="J273" s="2"/>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -4525,8 +5331,10 @@
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I274" s="2"/>
+      <c r="J274" s="2"/>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -4535,8 +5343,10 @@
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I275" s="2"/>
+      <c r="J275" s="2"/>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -4545,8 +5355,10 @@
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I276" s="2"/>
+      <c r="J276" s="2"/>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -4555,8 +5367,10 @@
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I277" s="2"/>
+      <c r="J277" s="2"/>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -4565,8 +5379,10 @@
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I278" s="2"/>
+      <c r="J278" s="2"/>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -4575,8 +5391,10 @@
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I279" s="2"/>
+      <c r="J279" s="2"/>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -4585,8 +5403,10 @@
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I280" s="2"/>
+      <c r="J280" s="2"/>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -4595,8 +5415,10 @@
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I281" s="2"/>
+      <c r="J281" s="2"/>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -4605,8 +5427,10 @@
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I282" s="2"/>
+      <c r="J282" s="2"/>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -4615,8 +5439,10 @@
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I283" s="2"/>
+      <c r="J283" s="2"/>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -4625,8 +5451,10 @@
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I284" s="2"/>
+      <c r="J284" s="2"/>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -4635,8 +5463,10 @@
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I285" s="2"/>
+      <c r="J285" s="2"/>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -4645,8 +5475,10 @@
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I286" s="2"/>
+      <c r="J286" s="2"/>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -4655,8 +5487,10 @@
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I287" s="2"/>
+      <c r="J287" s="2"/>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -4665,8 +5499,10 @@
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I288" s="2"/>
+      <c r="J288" s="2"/>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -4675,8 +5511,10 @@
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I289" s="2"/>
+      <c r="J289" s="2"/>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -4685,8 +5523,10 @@
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I290" s="2"/>
+      <c r="J290" s="2"/>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -4695,8 +5535,10 @@
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I291" s="2"/>
+      <c r="J291" s="2"/>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -4705,8 +5547,10 @@
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I292" s="2"/>
+      <c r="J292" s="2"/>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -4715,8 +5559,10 @@
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I293" s="2"/>
+      <c r="J293" s="2"/>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -4725,8 +5571,10 @@
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I294" s="2"/>
+      <c r="J294" s="2"/>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -4735,8 +5583,10 @@
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I295" s="2"/>
+      <c r="J295" s="2"/>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -4745,8 +5595,10 @@
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I296" s="2"/>
+      <c r="J296" s="2"/>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -4755,8 +5607,10 @@
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I297" s="2"/>
+      <c r="J297" s="2"/>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -4765,8 +5619,10 @@
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I298" s="2"/>
+      <c r="J298" s="2"/>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -4775,8 +5631,10 @@
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I299" s="2"/>
+      <c r="J299" s="2"/>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -4785,8 +5643,10 @@
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I300" s="2"/>
+      <c r="J300" s="2"/>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -4795,8 +5655,10 @@
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I301" s="2"/>
+      <c r="J301" s="2"/>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -4805,8 +5667,10 @@
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I302" s="2"/>
+      <c r="J302" s="2"/>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -4815,8 +5679,10 @@
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I303" s="2"/>
+      <c r="J303" s="2"/>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -4825,8 +5691,10 @@
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I304" s="2"/>
+      <c r="J304" s="2"/>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -4835,8 +5703,10 @@
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I305" s="2"/>
+      <c r="J305" s="2"/>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -4845,8 +5715,10 @@
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I306" s="2"/>
+      <c r="J306" s="2"/>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -4855,8 +5727,10 @@
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I307" s="2"/>
+      <c r="J307" s="2"/>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -4865,8 +5739,10 @@
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I308" s="2"/>
+      <c r="J308" s="2"/>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -4875,8 +5751,10 @@
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I309" s="2"/>
+      <c r="J309" s="2"/>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -4885,8 +5763,10 @@
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I310" s="2"/>
+      <c r="J310" s="2"/>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -4895,8 +5775,10 @@
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I311" s="2"/>
+      <c r="J311" s="2"/>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -4905,8 +5787,10 @@
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I312" s="2"/>
+      <c r="J312" s="2"/>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -4915,8 +5799,10 @@
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I313" s="2"/>
+      <c r="J313" s="2"/>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -4925,8 +5811,10 @@
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I314" s="2"/>
+      <c r="J314" s="2"/>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -4935,8 +5823,10 @@
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I315" s="2"/>
+      <c r="J315" s="2"/>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -4945,8 +5835,10 @@
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I316" s="2"/>
+      <c r="J316" s="2"/>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -4955,8 +5847,10 @@
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I317" s="2"/>
+      <c r="J317" s="2"/>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -4965,8 +5859,10 @@
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I318" s="2"/>
+      <c r="J318" s="2"/>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -4975,8 +5871,10 @@
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I319" s="2"/>
+      <c r="J319" s="2"/>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -4985,8 +5883,10 @@
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I320" s="2"/>
+      <c r="J320" s="2"/>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -4995,8 +5895,10 @@
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I321" s="2"/>
+      <c r="J321" s="2"/>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -5005,8 +5907,10 @@
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I322" s="2"/>
+      <c r="J322" s="2"/>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -5015,8 +5919,10 @@
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I323" s="2"/>
+      <c r="J323" s="2"/>
+    </row>
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -5025,8 +5931,10 @@
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I324" s="2"/>
+      <c r="J324" s="2"/>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -5035,8 +5943,10 @@
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I325" s="2"/>
+      <c r="J325" s="2"/>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -5045,8 +5955,10 @@
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I326" s="2"/>
+      <c r="J326" s="2"/>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -5055,8 +5967,10 @@
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I327" s="2"/>
+      <c r="J327" s="2"/>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -5065,8 +5979,10 @@
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I328" s="2"/>
+      <c r="J328" s="2"/>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -5075,8 +5991,10 @@
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I329" s="2"/>
+      <c r="J329" s="2"/>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -5085,8 +6003,10 @@
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I330" s="2"/>
+      <c r="J330" s="2"/>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -5095,8 +6015,10 @@
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I331" s="2"/>
+      <c r="J331" s="2"/>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -5105,8 +6027,10 @@
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I332" s="2"/>
+      <c r="J332" s="2"/>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -5115,8 +6039,10 @@
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I333" s="2"/>
+      <c r="J333" s="2"/>
+    </row>
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -5125,8 +6051,10 @@
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I334" s="2"/>
+      <c r="J334" s="2"/>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -5135,8 +6063,10 @@
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I335" s="2"/>
+      <c r="J335" s="2"/>
+    </row>
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -5145,8 +6075,10 @@
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I336" s="2"/>
+      <c r="J336" s="2"/>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -5155,8 +6087,10 @@
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I337" s="2"/>
+      <c r="J337" s="2"/>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -5165,8 +6099,10 @@
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I338" s="2"/>
+      <c r="J338" s="2"/>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -5175,8 +6111,10 @@
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I339" s="2"/>
+      <c r="J339" s="2"/>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -5185,8 +6123,10 @@
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I340" s="2"/>
+      <c r="J340" s="2"/>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -5195,8 +6135,10 @@
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I341" s="2"/>
+      <c r="J341" s="2"/>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -5205,8 +6147,10 @@
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I342" s="2"/>
+      <c r="J342" s="2"/>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -5215,8 +6159,10 @@
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I343" s="2"/>
+      <c r="J343" s="2"/>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -5225,8 +6171,10 @@
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I344" s="2"/>
+      <c r="J344" s="2"/>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -5235,8 +6183,10 @@
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I345" s="2"/>
+      <c r="J345" s="2"/>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -5245,8 +6195,10 @@
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I346" s="2"/>
+      <c r="J346" s="2"/>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -5255,8 +6207,10 @@
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I347" s="2"/>
+      <c r="J347" s="2"/>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -5265,8 +6219,10 @@
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I348" s="2"/>
+      <c r="J348" s="2"/>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -5275,8 +6231,10 @@
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I349" s="2"/>
+      <c r="J349" s="2"/>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -5285,8 +6243,10 @@
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I350" s="2"/>
+      <c r="J350" s="2"/>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -5295,8 +6255,10 @@
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I351" s="2"/>
+      <c r="J351" s="2"/>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -5305,8 +6267,10 @@
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I352" s="2"/>
+      <c r="J352" s="2"/>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -5315,8 +6279,10 @@
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I353" s="2"/>
+      <c r="J353" s="2"/>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -5325,8 +6291,10 @@
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I354" s="2"/>
+      <c r="J354" s="2"/>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -5335,8 +6303,10 @@
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I355" s="2"/>
+      <c r="J355" s="2"/>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -5345,8 +6315,10 @@
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I356" s="2"/>
+      <c r="J356" s="2"/>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -5355,8 +6327,10 @@
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I357" s="2"/>
+      <c r="J357" s="2"/>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -5365,8 +6339,10 @@
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I358" s="2"/>
+      <c r="J358" s="2"/>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -5375,8 +6351,10 @@
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I359" s="2"/>
+      <c r="J359" s="2"/>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -5385,8 +6363,10 @@
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I360" s="2"/>
+      <c r="J360" s="2"/>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -5395,8 +6375,10 @@
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I361" s="2"/>
+      <c r="J361" s="2"/>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -5405,8 +6387,10 @@
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I362" s="2"/>
+      <c r="J362" s="2"/>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -5415,8 +6399,10 @@
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I363" s="2"/>
+      <c r="J363" s="2"/>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -5425,8 +6411,10 @@
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I364" s="2"/>
+      <c r="J364" s="2"/>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -5435,8 +6423,10 @@
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I365" s="2"/>
+      <c r="J365" s="2"/>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -5445,8 +6435,10 @@
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I366" s="2"/>
+      <c r="J366" s="2"/>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -5455,8 +6447,10 @@
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I367" s="2"/>
+      <c r="J367" s="2"/>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -5465,8 +6459,10 @@
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I368" s="2"/>
+      <c r="J368" s="2"/>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -5475,8 +6471,10 @@
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I369" s="2"/>
+      <c r="J369" s="2"/>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -5485,8 +6483,10 @@
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I370" s="2"/>
+      <c r="J370" s="2"/>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -5495,8 +6495,10 @@
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I371" s="2"/>
+      <c r="J371" s="2"/>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -5505,8 +6507,10 @@
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I372" s="2"/>
+      <c r="J372" s="2"/>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -5515,8 +6519,10 @@
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
       <c r="H373" s="2"/>
-    </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I373" s="2"/>
+      <c r="J373" s="2"/>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -5525,8 +6531,10 @@
       <c r="F374" s="2"/>
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
-    </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I374" s="2"/>
+      <c r="J374" s="2"/>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -5535,8 +6543,10 @@
       <c r="F375" s="2"/>
       <c r="G375" s="2"/>
       <c r="H375" s="2"/>
-    </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I375" s="2"/>
+      <c r="J375" s="2"/>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -5545,8 +6555,10 @@
       <c r="F376" s="2"/>
       <c r="G376" s="2"/>
       <c r="H376" s="2"/>
-    </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I376" s="2"/>
+      <c r="J376" s="2"/>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -5555,8 +6567,10 @@
       <c r="F377" s="2"/>
       <c r="G377" s="2"/>
       <c r="H377" s="2"/>
-    </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I377" s="2"/>
+      <c r="J377" s="2"/>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -5565,8 +6579,10 @@
       <c r="F378" s="2"/>
       <c r="G378" s="2"/>
       <c r="H378" s="2"/>
-    </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I378" s="2"/>
+      <c r="J378" s="2"/>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -5575,8 +6591,10 @@
       <c r="F379" s="2"/>
       <c r="G379" s="2"/>
       <c r="H379" s="2"/>
-    </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I379" s="2"/>
+      <c r="J379" s="2"/>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -5585,8 +6603,10 @@
       <c r="F380" s="2"/>
       <c r="G380" s="2"/>
       <c r="H380" s="2"/>
-    </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I380" s="2"/>
+      <c r="J380" s="2"/>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -5595,8 +6615,10 @@
       <c r="F381" s="2"/>
       <c r="G381" s="2"/>
       <c r="H381" s="2"/>
-    </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I381" s="2"/>
+      <c r="J381" s="2"/>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -5605,8 +6627,10 @@
       <c r="F382" s="2"/>
       <c r="G382" s="2"/>
       <c r="H382" s="2"/>
-    </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I382" s="2"/>
+      <c r="J382" s="2"/>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -5615,8 +6639,10 @@
       <c r="F383" s="2"/>
       <c r="G383" s="2"/>
       <c r="H383" s="2"/>
-    </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I383" s="2"/>
+      <c r="J383" s="2"/>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -5625,8 +6651,10 @@
       <c r="F384" s="2"/>
       <c r="G384" s="2"/>
       <c r="H384" s="2"/>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I384" s="2"/>
+      <c r="J384" s="2"/>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -5635,8 +6663,10 @@
       <c r="F385" s="2"/>
       <c r="G385" s="2"/>
       <c r="H385" s="2"/>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I385" s="2"/>
+      <c r="J385" s="2"/>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -5645,8 +6675,10 @@
       <c r="F386" s="2"/>
       <c r="G386" s="2"/>
       <c r="H386" s="2"/>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I386" s="2"/>
+      <c r="J386" s="2"/>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -5655,8 +6687,10 @@
       <c r="F387" s="2"/>
       <c r="G387" s="2"/>
       <c r="H387" s="2"/>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I387" s="2"/>
+      <c r="J387" s="2"/>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -5665,8 +6699,10 @@
       <c r="F388" s="2"/>
       <c r="G388" s="2"/>
       <c r="H388" s="2"/>
-    </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I388" s="2"/>
+      <c r="J388" s="2"/>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -5675,8 +6711,10 @@
       <c r="F389" s="2"/>
       <c r="G389" s="2"/>
       <c r="H389" s="2"/>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I389" s="2"/>
+      <c r="J389" s="2"/>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -5685,8 +6723,10 @@
       <c r="F390" s="2"/>
       <c r="G390" s="2"/>
       <c r="H390" s="2"/>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I390" s="2"/>
+      <c r="J390" s="2"/>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -5695,8 +6735,10 @@
       <c r="F391" s="2"/>
       <c r="G391" s="2"/>
       <c r="H391" s="2"/>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I391" s="2"/>
+      <c r="J391" s="2"/>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -5705,8 +6747,10 @@
       <c r="F392" s="2"/>
       <c r="G392" s="2"/>
       <c r="H392" s="2"/>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I392" s="2"/>
+      <c r="J392" s="2"/>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -5715,8 +6759,10 @@
       <c r="F393" s="2"/>
       <c r="G393" s="2"/>
       <c r="H393" s="2"/>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I393" s="2"/>
+      <c r="J393" s="2"/>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -5725,8 +6771,10 @@
       <c r="F394" s="2"/>
       <c r="G394" s="2"/>
       <c r="H394" s="2"/>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I394" s="2"/>
+      <c r="J394" s="2"/>
+    </row>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -5735,8 +6783,10 @@
       <c r="F395" s="2"/>
       <c r="G395" s="2"/>
       <c r="H395" s="2"/>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I395" s="2"/>
+      <c r="J395" s="2"/>
+    </row>
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -5745,8 +6795,10 @@
       <c r="F396" s="2"/>
       <c r="G396" s="2"/>
       <c r="H396" s="2"/>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I396" s="2"/>
+      <c r="J396" s="2"/>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -5755,8 +6807,10 @@
       <c r="F397" s="2"/>
       <c r="G397" s="2"/>
       <c r="H397" s="2"/>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I397" s="2"/>
+      <c r="J397" s="2"/>
+    </row>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -5765,8 +6819,10 @@
       <c r="F398" s="2"/>
       <c r="G398" s="2"/>
       <c r="H398" s="2"/>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I398" s="2"/>
+      <c r="J398" s="2"/>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -5775,8 +6831,10 @@
       <c r="F399" s="2"/>
       <c r="G399" s="2"/>
       <c r="H399" s="2"/>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I399" s="2"/>
+      <c r="J399" s="2"/>
+    </row>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -5785,8 +6843,10 @@
       <c r="F400" s="2"/>
       <c r="G400" s="2"/>
       <c r="H400" s="2"/>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I400" s="2"/>
+      <c r="J400" s="2"/>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -5795,8 +6855,10 @@
       <c r="F401" s="2"/>
       <c r="G401" s="2"/>
       <c r="H401" s="2"/>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I401" s="2"/>
+      <c r="J401" s="2"/>
+    </row>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -5805,8 +6867,10 @@
       <c r="F402" s="2"/>
       <c r="G402" s="2"/>
       <c r="H402" s="2"/>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I402" s="2"/>
+      <c r="J402" s="2"/>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -5815,8 +6879,10 @@
       <c r="F403" s="2"/>
       <c r="G403" s="2"/>
       <c r="H403" s="2"/>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I403" s="2"/>
+      <c r="J403" s="2"/>
+    </row>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -5825,8 +6891,10 @@
       <c r="F404" s="2"/>
       <c r="G404" s="2"/>
       <c r="H404" s="2"/>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I404" s="2"/>
+      <c r="J404" s="2"/>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -5835,8 +6903,10 @@
       <c r="F405" s="2"/>
       <c r="G405" s="2"/>
       <c r="H405" s="2"/>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I405" s="2"/>
+      <c r="J405" s="2"/>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -5845,8 +6915,10 @@
       <c r="F406" s="2"/>
       <c r="G406" s="2"/>
       <c r="H406" s="2"/>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I406" s="2"/>
+      <c r="J406" s="2"/>
+    </row>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -5855,8 +6927,10 @@
       <c r="F407" s="2"/>
       <c r="G407" s="2"/>
       <c r="H407" s="2"/>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I407" s="2"/>
+      <c r="J407" s="2"/>
+    </row>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -5865,8 +6939,10 @@
       <c r="F408" s="2"/>
       <c r="G408" s="2"/>
       <c r="H408" s="2"/>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I408" s="2"/>
+      <c r="J408" s="2"/>
+    </row>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -5875,8 +6951,10 @@
       <c r="F409" s="2"/>
       <c r="G409" s="2"/>
       <c r="H409" s="2"/>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I409" s="2"/>
+      <c r="J409" s="2"/>
+    </row>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -5885,8 +6963,10 @@
       <c r="F410" s="2"/>
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I410" s="2"/>
+      <c r="J410" s="2"/>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -5895,8 +6975,10 @@
       <c r="F411" s="2"/>
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I411" s="2"/>
+      <c r="J411" s="2"/>
+    </row>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -5905,8 +6987,10 @@
       <c r="F412" s="2"/>
       <c r="G412" s="2"/>
       <c r="H412" s="2"/>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I412" s="2"/>
+      <c r="J412" s="2"/>
+    </row>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -5915,8 +6999,10 @@
       <c r="F413" s="2"/>
       <c r="G413" s="2"/>
       <c r="H413" s="2"/>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I413" s="2"/>
+      <c r="J413" s="2"/>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -5925,8 +7011,10 @@
       <c r="F414" s="2"/>
       <c r="G414" s="2"/>
       <c r="H414" s="2"/>
-    </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I414" s="2"/>
+      <c r="J414" s="2"/>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -5935,8 +7023,10 @@
       <c r="F415" s="2"/>
       <c r="G415" s="2"/>
       <c r="H415" s="2"/>
-    </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I415" s="2"/>
+      <c r="J415" s="2"/>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -5945,8 +7035,10 @@
       <c r="F416" s="2"/>
       <c r="G416" s="2"/>
       <c r="H416" s="2"/>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I416" s="2"/>
+      <c r="J416" s="2"/>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -5955,8 +7047,10 @@
       <c r="F417" s="2"/>
       <c r="G417" s="2"/>
       <c r="H417" s="2"/>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I417" s="2"/>
+      <c r="J417" s="2"/>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -5965,8 +7059,10 @@
       <c r="F418" s="2"/>
       <c r="G418" s="2"/>
       <c r="H418" s="2"/>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I418" s="2"/>
+      <c r="J418" s="2"/>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -5975,8 +7071,10 @@
       <c r="F419" s="2"/>
       <c r="G419" s="2"/>
       <c r="H419" s="2"/>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I419" s="2"/>
+      <c r="J419" s="2"/>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -5985,8 +7083,10 @@
       <c r="F420" s="2"/>
       <c r="G420" s="2"/>
       <c r="H420" s="2"/>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I420" s="2"/>
+      <c r="J420" s="2"/>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -5995,8 +7095,10 @@
       <c r="F421" s="2"/>
       <c r="G421" s="2"/>
       <c r="H421" s="2"/>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I421" s="2"/>
+      <c r="J421" s="2"/>
+    </row>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -6005,8 +7107,10 @@
       <c r="F422" s="2"/>
       <c r="G422" s="2"/>
       <c r="H422" s="2"/>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I422" s="2"/>
+      <c r="J422" s="2"/>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -6015,8 +7119,10 @@
       <c r="F423" s="2"/>
       <c r="G423" s="2"/>
       <c r="H423" s="2"/>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I423" s="2"/>
+      <c r="J423" s="2"/>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -6025,8 +7131,10 @@
       <c r="F424" s="2"/>
       <c r="G424" s="2"/>
       <c r="H424" s="2"/>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I424" s="2"/>
+      <c r="J424" s="2"/>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -6035,8 +7143,10 @@
       <c r="F425" s="2"/>
       <c r="G425" s="2"/>
       <c r="H425" s="2"/>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I425" s="2"/>
+      <c r="J425" s="2"/>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -6045,8 +7155,10 @@
       <c r="F426" s="2"/>
       <c r="G426" s="2"/>
       <c r="H426" s="2"/>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I426" s="2"/>
+      <c r="J426" s="2"/>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -6055,8 +7167,10 @@
       <c r="F427" s="2"/>
       <c r="G427" s="2"/>
       <c r="H427" s="2"/>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I427" s="2"/>
+      <c r="J427" s="2"/>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -6065,8 +7179,10 @@
       <c r="F428" s="2"/>
       <c r="G428" s="2"/>
       <c r="H428" s="2"/>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I428" s="2"/>
+      <c r="J428" s="2"/>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -6075,8 +7191,10 @@
       <c r="F429" s="2"/>
       <c r="G429" s="2"/>
       <c r="H429" s="2"/>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I429" s="2"/>
+      <c r="J429" s="2"/>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -6085,8 +7203,10 @@
       <c r="F430" s="2"/>
       <c r="G430" s="2"/>
       <c r="H430" s="2"/>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I430" s="2"/>
+      <c r="J430" s="2"/>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -6095,8 +7215,10 @@
       <c r="F431" s="2"/>
       <c r="G431" s="2"/>
       <c r="H431" s="2"/>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I431" s="2"/>
+      <c r="J431" s="2"/>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -6105,8 +7227,10 @@
       <c r="F432" s="2"/>
       <c r="G432" s="2"/>
       <c r="H432" s="2"/>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I432" s="2"/>
+      <c r="J432" s="2"/>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -6115,8 +7239,10 @@
       <c r="F433" s="2"/>
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I433" s="2"/>
+      <c r="J433" s="2"/>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -6125,8 +7251,10 @@
       <c r="F434" s="2"/>
       <c r="G434" s="2"/>
       <c r="H434" s="2"/>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I434" s="2"/>
+      <c r="J434" s="2"/>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -6135,8 +7263,10 @@
       <c r="F435" s="2"/>
       <c r="G435" s="2"/>
       <c r="H435" s="2"/>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I435" s="2"/>
+      <c r="J435" s="2"/>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -6145,8 +7275,10 @@
       <c r="F436" s="2"/>
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I436" s="2"/>
+      <c r="J436" s="2"/>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -6155,8 +7287,10 @@
       <c r="F437" s="2"/>
       <c r="G437" s="2"/>
       <c r="H437" s="2"/>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I437" s="2"/>
+      <c r="J437" s="2"/>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -6165,8 +7299,10 @@
       <c r="F438" s="2"/>
       <c r="G438" s="2"/>
       <c r="H438" s="2"/>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I438" s="2"/>
+      <c r="J438" s="2"/>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -6175,8 +7311,10 @@
       <c r="F439" s="2"/>
       <c r="G439" s="2"/>
       <c r="H439" s="2"/>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I439" s="2"/>
+      <c r="J439" s="2"/>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -6185,8 +7323,10 @@
       <c r="F440" s="2"/>
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I440" s="2"/>
+      <c r="J440" s="2"/>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -6195,8 +7335,10 @@
       <c r="F441" s="2"/>
       <c r="G441" s="2"/>
       <c r="H441" s="2"/>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I441" s="2"/>
+      <c r="J441" s="2"/>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -6205,8 +7347,10 @@
       <c r="F442" s="2"/>
       <c r="G442" s="2"/>
       <c r="H442" s="2"/>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I442" s="2"/>
+      <c r="J442" s="2"/>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -6215,8 +7359,10 @@
       <c r="F443" s="2"/>
       <c r="G443" s="2"/>
       <c r="H443" s="2"/>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I443" s="2"/>
+      <c r="J443" s="2"/>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -6225,8 +7371,10 @@
       <c r="F444" s="2"/>
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I444" s="2"/>
+      <c r="J444" s="2"/>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -6235,8 +7383,10 @@
       <c r="F445" s="2"/>
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
-    </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I445" s="2"/>
+      <c r="J445" s="2"/>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -6245,8 +7395,10 @@
       <c r="F446" s="2"/>
       <c r="G446" s="2"/>
       <c r="H446" s="2"/>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I446" s="2"/>
+      <c r="J446" s="2"/>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -6255,8 +7407,10 @@
       <c r="F447" s="2"/>
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I447" s="2"/>
+      <c r="J447" s="2"/>
+    </row>
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -6265,8 +7419,10 @@
       <c r="F448" s="2"/>
       <c r="G448" s="2"/>
       <c r="H448" s="2"/>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I448" s="2"/>
+      <c r="J448" s="2"/>
+    </row>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -6275,8 +7431,10 @@
       <c r="F449" s="2"/>
       <c r="G449" s="2"/>
       <c r="H449" s="2"/>
-    </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I449" s="2"/>
+      <c r="J449" s="2"/>
+    </row>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -6285,8 +7443,10 @@
       <c r="F450" s="2"/>
       <c r="G450" s="2"/>
       <c r="H450" s="2"/>
-    </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I450" s="2"/>
+      <c r="J450" s="2"/>
+    </row>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -6295,8 +7455,10 @@
       <c r="F451" s="2"/>
       <c r="G451" s="2"/>
       <c r="H451" s="2"/>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I451" s="2"/>
+      <c r="J451" s="2"/>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -6305,8 +7467,10 @@
       <c r="F452" s="2"/>
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I452" s="2"/>
+      <c r="J452" s="2"/>
+    </row>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -6315,8 +7479,10 @@
       <c r="F453" s="2"/>
       <c r="G453" s="2"/>
       <c r="H453" s="2"/>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I453" s="2"/>
+      <c r="J453" s="2"/>
+    </row>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -6325,8 +7491,10 @@
       <c r="F454" s="2"/>
       <c r="G454" s="2"/>
       <c r="H454" s="2"/>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I454" s="2"/>
+      <c r="J454" s="2"/>
+    </row>
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -6335,8 +7503,10 @@
       <c r="F455" s="2"/>
       <c r="G455" s="2"/>
       <c r="H455" s="2"/>
-    </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I455" s="2"/>
+      <c r="J455" s="2"/>
+    </row>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -6345,8 +7515,10 @@
       <c r="F456" s="2"/>
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I456" s="2"/>
+      <c r="J456" s="2"/>
+    </row>
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -6355,8 +7527,10 @@
       <c r="F457" s="2"/>
       <c r="G457" s="2"/>
       <c r="H457" s="2"/>
-    </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I457" s="2"/>
+      <c r="J457" s="2"/>
+    </row>
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -6365,8 +7539,10 @@
       <c r="F458" s="2"/>
       <c r="G458" s="2"/>
       <c r="H458" s="2"/>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I458" s="2"/>
+      <c r="J458" s="2"/>
+    </row>
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -6375,8 +7551,10 @@
       <c r="F459" s="2"/>
       <c r="G459" s="2"/>
       <c r="H459" s="2"/>
-    </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I459" s="2"/>
+      <c r="J459" s="2"/>
+    </row>
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -6385,8 +7563,10 @@
       <c r="F460" s="2"/>
       <c r="G460" s="2"/>
       <c r="H460" s="2"/>
-    </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I460" s="2"/>
+      <c r="J460" s="2"/>
+    </row>
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -6395,8 +7575,10 @@
       <c r="F461" s="2"/>
       <c r="G461" s="2"/>
       <c r="H461" s="2"/>
-    </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I461" s="2"/>
+      <c r="J461" s="2"/>
+    </row>
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -6405,8 +7587,10 @@
       <c r="F462" s="2"/>
       <c r="G462" s="2"/>
       <c r="H462" s="2"/>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I462" s="2"/>
+      <c r="J462" s="2"/>
+    </row>
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -6415,8 +7599,10 @@
       <c r="F463" s="2"/>
       <c r="G463" s="2"/>
       <c r="H463" s="2"/>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I463" s="2"/>
+      <c r="J463" s="2"/>
+    </row>
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -6425,8 +7611,10 @@
       <c r="F464" s="2"/>
       <c r="G464" s="2"/>
       <c r="H464" s="2"/>
-    </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I464" s="2"/>
+      <c r="J464" s="2"/>
+    </row>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -6435,8 +7623,10 @@
       <c r="F465" s="2"/>
       <c r="G465" s="2"/>
       <c r="H465" s="2"/>
-    </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I465" s="2"/>
+      <c r="J465" s="2"/>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -6445,8 +7635,10 @@
       <c r="F466" s="2"/>
       <c r="G466" s="2"/>
       <c r="H466" s="2"/>
-    </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I466" s="2"/>
+      <c r="J466" s="2"/>
+    </row>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -6455,8 +7647,10 @@
       <c r="F467" s="2"/>
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
-    </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I467" s="2"/>
+      <c r="J467" s="2"/>
+    </row>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -6465,8 +7659,10 @@
       <c r="F468" s="2"/>
       <c r="G468" s="2"/>
       <c r="H468" s="2"/>
-    </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I468" s="2"/>
+      <c r="J468" s="2"/>
+    </row>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -6475,8 +7671,10 @@
       <c r="F469" s="2"/>
       <c r="G469" s="2"/>
       <c r="H469" s="2"/>
-    </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I469" s="2"/>
+      <c r="J469" s="2"/>
+    </row>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -6485,8 +7683,10 @@
       <c r="F470" s="2"/>
       <c r="G470" s="2"/>
       <c r="H470" s="2"/>
-    </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I470" s="2"/>
+      <c r="J470" s="2"/>
+    </row>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -6495,8 +7695,10 @@
       <c r="F471" s="2"/>
       <c r="G471" s="2"/>
       <c r="H471" s="2"/>
-    </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I471" s="2"/>
+      <c r="J471" s="2"/>
+    </row>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -6505,8 +7707,10 @@
       <c r="F472" s="2"/>
       <c r="G472" s="2"/>
       <c r="H472" s="2"/>
-    </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I472" s="2"/>
+      <c r="J472" s="2"/>
+    </row>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -6515,8 +7719,10 @@
       <c r="F473" s="2"/>
       <c r="G473" s="2"/>
       <c r="H473" s="2"/>
-    </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I473" s="2"/>
+      <c r="J473" s="2"/>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -6525,8 +7731,10 @@
       <c r="F474" s="2"/>
       <c r="G474" s="2"/>
       <c r="H474" s="2"/>
-    </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I474" s="2"/>
+      <c r="J474" s="2"/>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -6535,8 +7743,10 @@
       <c r="F475" s="2"/>
       <c r="G475" s="2"/>
       <c r="H475" s="2"/>
-    </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I475" s="2"/>
+      <c r="J475" s="2"/>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -6545,8 +7755,10 @@
       <c r="F476" s="2"/>
       <c r="G476" s="2"/>
       <c r="H476" s="2"/>
-    </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I476" s="2"/>
+      <c r="J476" s="2"/>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -6555,8 +7767,10 @@
       <c r="F477" s="2"/>
       <c r="G477" s="2"/>
       <c r="H477" s="2"/>
-    </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I477" s="2"/>
+      <c r="J477" s="2"/>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -6565,8 +7779,10 @@
       <c r="F478" s="2"/>
       <c r="G478" s="2"/>
       <c r="H478" s="2"/>
-    </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I478" s="2"/>
+      <c r="J478" s="2"/>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -6575,8 +7791,10 @@
       <c r="F479" s="2"/>
       <c r="G479" s="2"/>
       <c r="H479" s="2"/>
-    </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I479" s="2"/>
+      <c r="J479" s="2"/>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -6585,8 +7803,10 @@
       <c r="F480" s="2"/>
       <c r="G480" s="2"/>
       <c r="H480" s="2"/>
-    </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I480" s="2"/>
+      <c r="J480" s="2"/>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -6595,8 +7815,10 @@
       <c r="F481" s="2"/>
       <c r="G481" s="2"/>
       <c r="H481" s="2"/>
-    </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I481" s="2"/>
+      <c r="J481" s="2"/>
+    </row>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -6605,8 +7827,10 @@
       <c r="F482" s="2"/>
       <c r="G482" s="2"/>
       <c r="H482" s="2"/>
-    </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I482" s="2"/>
+      <c r="J482" s="2"/>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -6615,8 +7839,10 @@
       <c r="F483" s="2"/>
       <c r="G483" s="2"/>
       <c r="H483" s="2"/>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I483" s="2"/>
+      <c r="J483" s="2"/>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -6625,8 +7851,10 @@
       <c r="F484" s="2"/>
       <c r="G484" s="2"/>
       <c r="H484" s="2"/>
-    </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I484" s="2"/>
+      <c r="J484" s="2"/>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -6635,8 +7863,10 @@
       <c r="F485" s="2"/>
       <c r="G485" s="2"/>
       <c r="H485" s="2"/>
-    </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I485" s="2"/>
+      <c r="J485" s="2"/>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -6645,8 +7875,10 @@
       <c r="F486" s="2"/>
       <c r="G486" s="2"/>
       <c r="H486" s="2"/>
-    </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I486" s="2"/>
+      <c r="J486" s="2"/>
+    </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -6655,8 +7887,10 @@
       <c r="F487" s="2"/>
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I487" s="2"/>
+      <c r="J487" s="2"/>
+    </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -6665,8 +7899,10 @@
       <c r="F488" s="2"/>
       <c r="G488" s="2"/>
       <c r="H488" s="2"/>
-    </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I488" s="2"/>
+      <c r="J488" s="2"/>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -6675,8 +7911,10 @@
       <c r="F489" s="2"/>
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
-    </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I489" s="2"/>
+      <c r="J489" s="2"/>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -6685,8 +7923,10 @@
       <c r="F490" s="2"/>
       <c r="G490" s="2"/>
       <c r="H490" s="2"/>
-    </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I490" s="2"/>
+      <c r="J490" s="2"/>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -6695,8 +7935,10 @@
       <c r="F491" s="2"/>
       <c r="G491" s="2"/>
       <c r="H491" s="2"/>
-    </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I491" s="2"/>
+      <c r="J491" s="2"/>
+    </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -6705,8 +7947,10 @@
       <c r="F492" s="2"/>
       <c r="G492" s="2"/>
       <c r="H492" s="2"/>
-    </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I492" s="2"/>
+      <c r="J492" s="2"/>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -6715,8 +7959,10 @@
       <c r="F493" s="2"/>
       <c r="G493" s="2"/>
       <c r="H493" s="2"/>
-    </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I493" s="2"/>
+      <c r="J493" s="2"/>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -6725,8 +7971,10 @@
       <c r="F494" s="2"/>
       <c r="G494" s="2"/>
       <c r="H494" s="2"/>
-    </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I494" s="2"/>
+      <c r="J494" s="2"/>
+    </row>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -6735,8 +7983,10 @@
       <c r="F495" s="2"/>
       <c r="G495" s="2"/>
       <c r="H495" s="2"/>
-    </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I495" s="2"/>
+      <c r="J495" s="2"/>
+    </row>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -6745,8 +7995,10 @@
       <c r="F496" s="2"/>
       <c r="G496" s="2"/>
       <c r="H496" s="2"/>
-    </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I496" s="2"/>
+      <c r="J496" s="2"/>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -6755,8 +8007,10 @@
       <c r="F497" s="2"/>
       <c r="G497" s="2"/>
       <c r="H497" s="2"/>
-    </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I497" s="2"/>
+      <c r="J497" s="2"/>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -6765,8 +8019,10 @@
       <c r="F498" s="2"/>
       <c r="G498" s="2"/>
       <c r="H498" s="2"/>
-    </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I498" s="2"/>
+      <c r="J498" s="2"/>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -6775,8 +8031,10 @@
       <c r="F499" s="2"/>
       <c r="G499" s="2"/>
       <c r="H499" s="2"/>
-    </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I499" s="2"/>
+      <c r="J499" s="2"/>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -6785,6 +8043,8 @@
       <c r="F500" s="2"/>
       <c r="G500" s="2"/>
       <c r="H500" s="2"/>
+      <c r="I500" s="2"/>
+      <c r="J500" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -6798,10 +8058,16 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Producto no valido" error="Seleccione un producto de la lista." xr:uid="{ED3FBE40-67ED-4FE7-9580-6708A76A5F38}">
           <x14:formula1>
-            <xm:f>Catalogo!$A$2:$A$14</xm:f>
+            <xm:f>Catalogo!$H$2:$H$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H500</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{D83E1DC8-A2D6-4C03-80A4-D9E29D4F690D}">
+          <x14:formula1>
+            <xm:f>Catalogo!$A$2:$A$21</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A500</xm:sqref>
         </x14:dataValidation>
@@ -6814,7 +8080,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -6828,7 +8094,7 @@
     <col min="10" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -6860,7 +8126,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
@@ -6892,7 +8158,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
@@ -6919,24 +8185,24 @@
         <v>36</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="360" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>33</v>
@@ -6949,24 +8215,24 @@
         <v>42</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="255" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>33</v>
@@ -6979,21 +8245,21 @@
         <v>36</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>41</v>
@@ -7009,24 +8275,24 @@
         <v>36</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="375" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="360" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
@@ -7039,24 +8305,24 @@
         <v>42</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>33</v>
@@ -7074,21 +8340,21 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>33</v>
@@ -7103,24 +8369,24 @@
         <v>36</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>33</v>
@@ -7133,24 +8399,24 @@
         <v>42</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="240" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>33</v>
@@ -7159,32 +8425,28 @@
       <c r="H11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automatizado</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Disponible en la hoja Control (REC-OTP-001). Mismo escenario de 38529; el evento del OTP no se ve en la app (verificacion fuera de la UI). En la app el OTP se pide despues de la clave nueva</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+      <c r="I11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>33</v>
@@ -7195,68 +8457,66 @@
       <c r="H12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Automatizado</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Disponible en la hoja Control (REC-001). RN-R07 confirmada. En la app la clave nueva se pide antes del OTP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+      <c r="I12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>35</v>
@@ -7265,30 +8525,30 @@
         <v>36</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>35</v>
@@ -7297,54 +8557,54 @@
         <v>36</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="255" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>33</v>
@@ -7354,25 +8614,27 @@
         <v>35</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>33</v>
@@ -7385,24 +8647,24 @@
         <v>36</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>33</v>
@@ -7415,174 +8677,184 @@
         <v>36</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="225" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" ht="210" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>35</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>33</v>
@@ -7592,31 +8864,31 @@
         <v>35</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>35</v>
@@ -7625,7 +8897,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -7636,226 +8908,242 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="10"/>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B6" s="10"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-    </row>
-    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="B16" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
-    </row>
-    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+    </row>
+    <row r="18" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="10"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B26" s="10" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B27" s="10" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+    </row>
+    <row r="29" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B29" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="10" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="B32" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-    </row>
-    <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10"/>
-    </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>220</v>
+      <c r="B33" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -7865,30 +9153,33 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="H1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7899,18 +9190,21 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+      <c r="H2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -7919,260 +9213,391 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+      <c r="H3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>195</v>
       </c>
-      <c r="E4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>210</v>
-      </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>212</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>222</v>
-      </c>
-      <c r="E6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>229</v>
-      </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10">
+        <v>38698</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13">
+        <v>38702</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>235</v>
       </c>
-      <c r="E8" t="s">
-        <v>212</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="E15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16">
+        <v>38705</v>
+      </c>
+      <c r="C16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
+        <v>268</v>
+      </c>
+      <c r="E16" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B17">
+        <v>38706</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18">
+        <v>38707</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" t="s">
+        <v>179</v>
+      </c>
+      <c r="F18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19">
+        <v>38708</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>277</v>
+      </c>
+      <c r="E19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20">
+        <v>38709</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>280</v>
+      </c>
+      <c r="E20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>240</v>
       </c>
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" t="s">
         <v>241</v>
       </c>
-      <c r="E9" t="s">
-        <v>188</v>
-      </c>
-      <c r="F9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>247</v>
-      </c>
-      <c r="E10" t="s">
-        <v>188</v>
-      </c>
-      <c r="F10" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>252</v>
-      </c>
-      <c r="E11" t="s">
-        <v>188</v>
-      </c>
-      <c r="F11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>256</v>
-      </c>
-      <c r="B12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E12" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38529 - Recuperacion de clave con CC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38529</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recuperacion de clave</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@38529</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TipoDocumento (CC)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS). Clave = la nueva: vacia se genera segun RN-R07 y distinta de la actual; si se informa debe cumplir RN-R07. OTP: vacio = 000000. Cambia la clave del cliente: el listado guarda la nueva al confirmar; si falla tras enviar el cambio queda FALLIDO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38526 - OTP en la recuperacion de clave</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38526</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recuperacion de clave</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@38526</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TipoDocumento (CC)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mismo escenario y reglas de 38529 (el OTP es un paso del flujo de recuperacion). El evento "Recuperacion de contrasena" del OTP no se ve en la app: se verifica fuera de la UI.</t>
-        </is>
+      <c r="E21" t="s">
+        <v>179</v>
+      </c>
+      <c r="F21" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+    <sortCondition ref="A2"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/control/Control_Ejecucion.xlsx
+++ b/control/Control_Ejecucion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GreenSQA\MiBanco\ATM-APP_MiBanco\ATM_AppMovil_MiBanco\control\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GreenSQA\AppData\Local\Temp\claude\c--ATM-AppMovil-MiBanco\4bd799e8-9fec-418b-87c7-f5e93e1a90ec\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46CAC0F-64C8-435E-9141-33C09006CDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4013C14B-A490-4038-BF0F-EE797F1F5911}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="327">
   <si>
     <t>Caso</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>REG-001</t>
-  </si>
-  <si>
-    <t>SI</t>
   </si>
   <si>
     <t>CC</t>
@@ -937,9 +934,6 @@
     <t>Numero de documento (6 a 11 digitos). AUTO o vacio: en registro toma un cliente DISPONIBLE del listado datos/pool_clientes.xlsx; en login toma un cliente REGISTRADO con su clave (no lo consume). Los casos de SMS solo toman clientes con LINEA_SMS = SI y los demas casos nunca los toman.</t>
   </si>
   <si>
-    <t>Clave de 4 digitos. Registro exitoso: vacia = se genera una valida segun RN-R07; si se informa debe cumplir RN-R07. Login: vacia = la clave guardada en el listado; con AUTO debe ir vacia.</t>
-  </si>
-  <si>
     <t>38503 - SMS por registro exitoso con CE</t>
   </si>
   <si>
@@ -1295,13 +1289,58 @@
   </si>
   <si>
     <t>Skeleton (Cargando...) mientras el Home obtiene los saldos; se observa por DevTools del WebView</t>
+  </si>
+  <si>
+    <t>LOG-002</t>
+  </si>
+  <si>
+    <t>REG-004</t>
+  </si>
+  <si>
+    <t>REG-005</t>
+  </si>
+  <si>
+    <t>Clave de 4 digitos. Con NumDocumento AUTO: dejar vacia (registro y recuperacion generan una valida segun RN-R07; login y Home usan la clave guardada en el listado). Con un numero de documento informado la Clave es OBLIGATORIA: la que se crea en el registro, la actual del cliente en login/Home/productos o la nueva en la recuperacion; si falta, la fila queda NO EJECUTADA. En registro y recuperacion debe cumplir RN-R07.</t>
+  </si>
+  <si>
+    <t>LOG-005</t>
+  </si>
+  <si>
+    <t>SALU-PREG-002</t>
+  </si>
+  <si>
+    <t>HOME-ACC-003</t>
+  </si>
+  <si>
+    <t>PROD-PRA-002</t>
+  </si>
+  <si>
+    <t>MENU-INF-001</t>
+  </si>
+  <si>
+    <t>PROD-ROT-002</t>
+  </si>
+  <si>
+    <t>PROD-LIB-002</t>
+  </si>
+  <si>
+    <t>PROD-CORR-002</t>
+  </si>
+  <si>
+    <t>PROD-AHO-002</t>
+  </si>
+  <si>
+    <t>HOME-ACC-004</t>
+  </si>
+  <si>
+    <t>2658679.07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1325,6 +1364,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1382,7 +1428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1411,6 +1457,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1714,19 +1761,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="16.77734375" customWidth="1"/>
+    <col min="8" max="9" width="16.81640625" customWidth="1"/>
     <col min="10" max="10" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1749,16 +1796,16 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1766,779 +1813,953 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="B11" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="C12" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="C13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="C14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="B15" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="C16" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="H40" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2550,7 +2771,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2562,7 +2783,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2574,7 +2795,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2586,7 +2807,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2598,7 +2819,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2610,7 +2831,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2622,7 +2843,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2634,7 +2855,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2646,7 +2867,7 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2658,7 +2879,7 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2670,7 +2891,7 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2682,7 +2903,7 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2694,7 +2915,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2706,7 +2927,7 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2718,7 +2939,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2730,7 +2951,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2742,7 +2963,7 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2754,7 +2975,7 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2766,7 +2987,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2778,7 +2999,7 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2790,7 +3011,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2802,7 +3023,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2814,7 +3035,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2826,7 +3047,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2838,7 +3059,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2850,7 +3071,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2862,7 +3083,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2874,7 +3095,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -2886,7 +3107,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2898,7 +3119,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -2910,7 +3131,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -2922,7 +3143,7 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -2934,7 +3155,7 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2946,7 +3167,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -2958,7 +3179,7 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -2970,7 +3191,7 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -2982,7 +3203,7 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -2994,7 +3215,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3006,7 +3227,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3018,7 +3239,7 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3030,7 +3251,7 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3042,7 +3263,7 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3054,7 +3275,7 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3066,7 +3287,7 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3078,7 +3299,7 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -3090,7 +3311,7 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3102,7 +3323,7 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3114,7 +3335,7 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -3126,7 +3347,7 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -3138,7 +3359,7 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -3150,7 +3371,7 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -3162,7 +3383,7 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -3174,7 +3395,7 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -3186,7 +3407,7 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3198,7 +3419,7 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3210,7 +3431,7 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -3222,7 +3443,7 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -3234,7 +3455,7 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -3246,7 +3467,7 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -3258,7 +3479,7 @@
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -3270,7 +3491,7 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -3282,7 +3503,7 @@
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -3294,7 +3515,7 @@
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -3306,7 +3527,7 @@
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -3318,7 +3539,7 @@
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -3330,7 +3551,7 @@
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -3342,7 +3563,7 @@
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -3354,7 +3575,7 @@
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -3366,7 +3587,7 @@
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -3378,7 +3599,7 @@
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -3390,7 +3611,7 @@
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -3402,7 +3623,7 @@
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -3414,7 +3635,7 @@
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -3426,7 +3647,7 @@
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -3438,7 +3659,7 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -3450,7 +3671,7 @@
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -3462,7 +3683,7 @@
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -3474,7 +3695,7 @@
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -3486,7 +3707,7 @@
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -3498,7 +3719,7 @@
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -3510,7 +3731,7 @@
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -3522,7 +3743,7 @@
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -3534,7 +3755,7 @@
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -3546,7 +3767,7 @@
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -3558,7 +3779,7 @@
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -3570,7 +3791,7 @@
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -3582,7 +3803,7 @@
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -3594,7 +3815,7 @@
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -3606,7 +3827,7 @@
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -3618,7 +3839,7 @@
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -3630,7 +3851,7 @@
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -3642,7 +3863,7 @@
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -3654,7 +3875,7 @@
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -3666,7 +3887,7 @@
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -3678,7 +3899,7 @@
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -3690,7 +3911,7 @@
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -3702,7 +3923,7 @@
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -3714,7 +3935,7 @@
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -3726,7 +3947,7 @@
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -3738,7 +3959,7 @@
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -3750,7 +3971,7 @@
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -3762,7 +3983,7 @@
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -3774,7 +3995,7 @@
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -3786,7 +4007,7 @@
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -3798,7 +4019,7 @@
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -3810,7 +4031,7 @@
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -3822,7 +4043,7 @@
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -3834,7 +4055,7 @@
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -3846,7 +4067,7 @@
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -3858,7 +4079,7 @@
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -3870,7 +4091,7 @@
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -3882,7 +4103,7 @@
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -3894,7 +4115,7 @@
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -3906,7 +4127,7 @@
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -3918,7 +4139,7 @@
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -3930,7 +4151,7 @@
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -3942,7 +4163,7 @@
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -3954,7 +4175,7 @@
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -3966,7 +4187,7 @@
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -3978,7 +4199,7 @@
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -3990,7 +4211,7 @@
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -4002,7 +4223,7 @@
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -4014,7 +4235,7 @@
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -4026,7 +4247,7 @@
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -4038,7 +4259,7 @@
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -4050,7 +4271,7 @@
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -4062,7 +4283,7 @@
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -4074,7 +4295,7 @@
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -4086,7 +4307,7 @@
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -4098,7 +4319,7 @@
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -4110,7 +4331,7 @@
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -4122,7 +4343,7 @@
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -4134,7 +4355,7 @@
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -4146,7 +4367,7 @@
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -4158,7 +4379,7 @@
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -4170,7 +4391,7 @@
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -4182,7 +4403,7 @@
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -4194,7 +4415,7 @@
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -4206,7 +4427,7 @@
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -4218,7 +4439,7 @@
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -4230,7 +4451,7 @@
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -4242,7 +4463,7 @@
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -4254,7 +4475,7 @@
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -4266,7 +4487,7 @@
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -4278,7 +4499,7 @@
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -4290,7 +4511,7 @@
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -4302,7 +4523,7 @@
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -4314,7 +4535,7 @@
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -4326,7 +4547,7 @@
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -4338,7 +4559,7 @@
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -4350,7 +4571,7 @@
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -4362,7 +4583,7 @@
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -4374,7 +4595,7 @@
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -4386,7 +4607,7 @@
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -4398,7 +4619,7 @@
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -4410,7 +4631,7 @@
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -4422,7 +4643,7 @@
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -4434,7 +4655,7 @@
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -4446,7 +4667,7 @@
       <c r="I200" s="2"/>
       <c r="J200" s="2"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -4458,7 +4679,7 @@
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -4470,7 +4691,7 @@
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -4482,7 +4703,7 @@
       <c r="I203" s="2"/>
       <c r="J203" s="2"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -4494,7 +4715,7 @@
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -4506,7 +4727,7 @@
       <c r="I205" s="2"/>
       <c r="J205" s="2"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -4518,7 +4739,7 @@
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -4530,7 +4751,7 @@
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -4542,7 +4763,7 @@
       <c r="I208" s="2"/>
       <c r="J208" s="2"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -4554,7 +4775,7 @@
       <c r="I209" s="2"/>
       <c r="J209" s="2"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -4566,7 +4787,7 @@
       <c r="I210" s="2"/>
       <c r="J210" s="2"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -4578,7 +4799,7 @@
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -4590,7 +4811,7 @@
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -4602,7 +4823,7 @@
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -4614,7 +4835,7 @@
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -4626,7 +4847,7 @@
       <c r="I215" s="2"/>
       <c r="J215" s="2"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -4638,7 +4859,7 @@
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -4650,7 +4871,7 @@
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -4662,7 +4883,7 @@
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -4674,7 +4895,7 @@
       <c r="I219" s="2"/>
       <c r="J219" s="2"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -4686,7 +4907,7 @@
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -4698,7 +4919,7 @@
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -4710,7 +4931,7 @@
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -4722,7 +4943,7 @@
       <c r="I223" s="2"/>
       <c r="J223" s="2"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -4734,7 +4955,7 @@
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -4746,7 +4967,7 @@
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -4758,7 +4979,7 @@
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -4770,7 +4991,7 @@
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -4782,7 +5003,7 @@
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -4794,7 +5015,7 @@
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -4806,7 +5027,7 @@
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -4818,7 +5039,7 @@
       <c r="I231" s="2"/>
       <c r="J231" s="2"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -4830,7 +5051,7 @@
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -4842,7 +5063,7 @@
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -4854,7 +5075,7 @@
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -4866,7 +5087,7 @@
       <c r="I235" s="2"/>
       <c r="J235" s="2"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -4878,7 +5099,7 @@
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -4890,7 +5111,7 @@
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -4902,7 +5123,7 @@
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -4914,7 +5135,7 @@
       <c r="I239" s="2"/>
       <c r="J239" s="2"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -4926,7 +5147,7 @@
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -4938,7 +5159,7 @@
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -4950,7 +5171,7 @@
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -4962,7 +5183,7 @@
       <c r="I243" s="2"/>
       <c r="J243" s="2"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -4974,7 +5195,7 @@
       <c r="I244" s="2"/>
       <c r="J244" s="2"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -4986,7 +5207,7 @@
       <c r="I245" s="2"/>
       <c r="J245" s="2"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -4998,7 +5219,7 @@
       <c r="I246" s="2"/>
       <c r="J246" s="2"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -5010,7 +5231,7 @@
       <c r="I247" s="2"/>
       <c r="J247" s="2"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -5022,7 +5243,7 @@
       <c r="I248" s="2"/>
       <c r="J248" s="2"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -5034,7 +5255,7 @@
       <c r="I249" s="2"/>
       <c r="J249" s="2"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -5046,7 +5267,7 @@
       <c r="I250" s="2"/>
       <c r="J250" s="2"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -5058,7 +5279,7 @@
       <c r="I251" s="2"/>
       <c r="J251" s="2"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -5070,7 +5291,7 @@
       <c r="I252" s="2"/>
       <c r="J252" s="2"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -5082,7 +5303,7 @@
       <c r="I253" s="2"/>
       <c r="J253" s="2"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -5094,7 +5315,7 @@
       <c r="I254" s="2"/>
       <c r="J254" s="2"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -5106,7 +5327,7 @@
       <c r="I255" s="2"/>
       <c r="J255" s="2"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -5118,7 +5339,7 @@
       <c r="I256" s="2"/>
       <c r="J256" s="2"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -5130,7 +5351,7 @@
       <c r="I257" s="2"/>
       <c r="J257" s="2"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -5142,7 +5363,7 @@
       <c r="I258" s="2"/>
       <c r="J258" s="2"/>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -5154,7 +5375,7 @@
       <c r="I259" s="2"/>
       <c r="J259" s="2"/>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -5166,7 +5387,7 @@
       <c r="I260" s="2"/>
       <c r="J260" s="2"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -5178,7 +5399,7 @@
       <c r="I261" s="2"/>
       <c r="J261" s="2"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -5190,7 +5411,7 @@
       <c r="I262" s="2"/>
       <c r="J262" s="2"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -5202,7 +5423,7 @@
       <c r="I263" s="2"/>
       <c r="J263" s="2"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -5214,7 +5435,7 @@
       <c r="I264" s="2"/>
       <c r="J264" s="2"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -5226,7 +5447,7 @@
       <c r="I265" s="2"/>
       <c r="J265" s="2"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -5238,7 +5459,7 @@
       <c r="I266" s="2"/>
       <c r="J266" s="2"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -5250,7 +5471,7 @@
       <c r="I267" s="2"/>
       <c r="J267" s="2"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -5262,7 +5483,7 @@
       <c r="I268" s="2"/>
       <c r="J268" s="2"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -5274,7 +5495,7 @@
       <c r="I269" s="2"/>
       <c r="J269" s="2"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -5286,7 +5507,7 @@
       <c r="I270" s="2"/>
       <c r="J270" s="2"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -5298,7 +5519,7 @@
       <c r="I271" s="2"/>
       <c r="J271" s="2"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -5310,7 +5531,7 @@
       <c r="I272" s="2"/>
       <c r="J272" s="2"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -5322,7 +5543,7 @@
       <c r="I273" s="2"/>
       <c r="J273" s="2"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -5334,7 +5555,7 @@
       <c r="I274" s="2"/>
       <c r="J274" s="2"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -5346,7 +5567,7 @@
       <c r="I275" s="2"/>
       <c r="J275" s="2"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -5358,7 +5579,7 @@
       <c r="I276" s="2"/>
       <c r="J276" s="2"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -5370,7 +5591,7 @@
       <c r="I277" s="2"/>
       <c r="J277" s="2"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -5382,7 +5603,7 @@
       <c r="I278" s="2"/>
       <c r="J278" s="2"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -5394,7 +5615,7 @@
       <c r="I279" s="2"/>
       <c r="J279" s="2"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -5406,7 +5627,7 @@
       <c r="I280" s="2"/>
       <c r="J280" s="2"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -5418,7 +5639,7 @@
       <c r="I281" s="2"/>
       <c r="J281" s="2"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -5430,7 +5651,7 @@
       <c r="I282" s="2"/>
       <c r="J282" s="2"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -5442,7 +5663,7 @@
       <c r="I283" s="2"/>
       <c r="J283" s="2"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -5454,7 +5675,7 @@
       <c r="I284" s="2"/>
       <c r="J284" s="2"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -5466,7 +5687,7 @@
       <c r="I285" s="2"/>
       <c r="J285" s="2"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -5478,7 +5699,7 @@
       <c r="I286" s="2"/>
       <c r="J286" s="2"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -5490,7 +5711,7 @@
       <c r="I287" s="2"/>
       <c r="J287" s="2"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -5502,7 +5723,7 @@
       <c r="I288" s="2"/>
       <c r="J288" s="2"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -5514,7 +5735,7 @@
       <c r="I289" s="2"/>
       <c r="J289" s="2"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -5526,7 +5747,7 @@
       <c r="I290" s="2"/>
       <c r="J290" s="2"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -5538,7 +5759,7 @@
       <c r="I291" s="2"/>
       <c r="J291" s="2"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -5550,7 +5771,7 @@
       <c r="I292" s="2"/>
       <c r="J292" s="2"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -5562,7 +5783,7 @@
       <c r="I293" s="2"/>
       <c r="J293" s="2"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -5574,7 +5795,7 @@
       <c r="I294" s="2"/>
       <c r="J294" s="2"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -5586,7 +5807,7 @@
       <c r="I295" s="2"/>
       <c r="J295" s="2"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -5598,7 +5819,7 @@
       <c r="I296" s="2"/>
       <c r="J296" s="2"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -5610,7 +5831,7 @@
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -5622,7 +5843,7 @@
       <c r="I298" s="2"/>
       <c r="J298" s="2"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -5634,7 +5855,7 @@
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -5646,7 +5867,7 @@
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -5658,7 +5879,7 @@
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -5670,7 +5891,7 @@
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -5682,7 +5903,7 @@
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -5694,7 +5915,7 @@
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -5706,7 +5927,7 @@
       <c r="I305" s="2"/>
       <c r="J305" s="2"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -5718,7 +5939,7 @@
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -5730,7 +5951,7 @@
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -5742,7 +5963,7 @@
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -5754,7 +5975,7 @@
       <c r="I309" s="2"/>
       <c r="J309" s="2"/>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -5766,7 +5987,7 @@
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -5778,7 +5999,7 @@
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -5790,7 +6011,7 @@
       <c r="I312" s="2"/>
       <c r="J312" s="2"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -5802,7 +6023,7 @@
       <c r="I313" s="2"/>
       <c r="J313" s="2"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -5814,7 +6035,7 @@
       <c r="I314" s="2"/>
       <c r="J314" s="2"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -5826,7 +6047,7 @@
       <c r="I315" s="2"/>
       <c r="J315" s="2"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -5838,7 +6059,7 @@
       <c r="I316" s="2"/>
       <c r="J316" s="2"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -5850,7 +6071,7 @@
       <c r="I317" s="2"/>
       <c r="J317" s="2"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -5862,7 +6083,7 @@
       <c r="I318" s="2"/>
       <c r="J318" s="2"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -5874,7 +6095,7 @@
       <c r="I319" s="2"/>
       <c r="J319" s="2"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -5886,7 +6107,7 @@
       <c r="I320" s="2"/>
       <c r="J320" s="2"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -5898,7 +6119,7 @@
       <c r="I321" s="2"/>
       <c r="J321" s="2"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -5910,7 +6131,7 @@
       <c r="I322" s="2"/>
       <c r="J322" s="2"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -5922,7 +6143,7 @@
       <c r="I323" s="2"/>
       <c r="J323" s="2"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -5934,7 +6155,7 @@
       <c r="I324" s="2"/>
       <c r="J324" s="2"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -5946,7 +6167,7 @@
       <c r="I325" s="2"/>
       <c r="J325" s="2"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -5958,7 +6179,7 @@
       <c r="I326" s="2"/>
       <c r="J326" s="2"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -5970,7 +6191,7 @@
       <c r="I327" s="2"/>
       <c r="J327" s="2"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -5982,7 +6203,7 @@
       <c r="I328" s="2"/>
       <c r="J328" s="2"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -5994,7 +6215,7 @@
       <c r="I329" s="2"/>
       <c r="J329" s="2"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -6006,7 +6227,7 @@
       <c r="I330" s="2"/>
       <c r="J330" s="2"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -6018,7 +6239,7 @@
       <c r="I331" s="2"/>
       <c r="J331" s="2"/>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -6030,7 +6251,7 @@
       <c r="I332" s="2"/>
       <c r="J332" s="2"/>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -6042,7 +6263,7 @@
       <c r="I333" s="2"/>
       <c r="J333" s="2"/>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -6054,7 +6275,7 @@
       <c r="I334" s="2"/>
       <c r="J334" s="2"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -6066,7 +6287,7 @@
       <c r="I335" s="2"/>
       <c r="J335" s="2"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -6078,7 +6299,7 @@
       <c r="I336" s="2"/>
       <c r="J336" s="2"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -6090,7 +6311,7 @@
       <c r="I337" s="2"/>
       <c r="J337" s="2"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -6102,7 +6323,7 @@
       <c r="I338" s="2"/>
       <c r="J338" s="2"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -6114,7 +6335,7 @@
       <c r="I339" s="2"/>
       <c r="J339" s="2"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -6126,7 +6347,7 @@
       <c r="I340" s="2"/>
       <c r="J340" s="2"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -6138,7 +6359,7 @@
       <c r="I341" s="2"/>
       <c r="J341" s="2"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -6150,7 +6371,7 @@
       <c r="I342" s="2"/>
       <c r="J342" s="2"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -6162,7 +6383,7 @@
       <c r="I343" s="2"/>
       <c r="J343" s="2"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -6174,7 +6395,7 @@
       <c r="I344" s="2"/>
       <c r="J344" s="2"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -6186,7 +6407,7 @@
       <c r="I345" s="2"/>
       <c r="J345" s="2"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -6198,7 +6419,7 @@
       <c r="I346" s="2"/>
       <c r="J346" s="2"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -6210,7 +6431,7 @@
       <c r="I347" s="2"/>
       <c r="J347" s="2"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -6222,7 +6443,7 @@
       <c r="I348" s="2"/>
       <c r="J348" s="2"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -6234,7 +6455,7 @@
       <c r="I349" s="2"/>
       <c r="J349" s="2"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -6246,7 +6467,7 @@
       <c r="I350" s="2"/>
       <c r="J350" s="2"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -6258,7 +6479,7 @@
       <c r="I351" s="2"/>
       <c r="J351" s="2"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -6270,7 +6491,7 @@
       <c r="I352" s="2"/>
       <c r="J352" s="2"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -6282,7 +6503,7 @@
       <c r="I353" s="2"/>
       <c r="J353" s="2"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -6294,7 +6515,7 @@
       <c r="I354" s="2"/>
       <c r="J354" s="2"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -6306,7 +6527,7 @@
       <c r="I355" s="2"/>
       <c r="J355" s="2"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -6318,7 +6539,7 @@
       <c r="I356" s="2"/>
       <c r="J356" s="2"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -6330,7 +6551,7 @@
       <c r="I357" s="2"/>
       <c r="J357" s="2"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -6342,7 +6563,7 @@
       <c r="I358" s="2"/>
       <c r="J358" s="2"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -6354,7 +6575,7 @@
       <c r="I359" s="2"/>
       <c r="J359" s="2"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -6366,7 +6587,7 @@
       <c r="I360" s="2"/>
       <c r="J360" s="2"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -6378,7 +6599,7 @@
       <c r="I361" s="2"/>
       <c r="J361" s="2"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -6390,7 +6611,7 @@
       <c r="I362" s="2"/>
       <c r="J362" s="2"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -6402,7 +6623,7 @@
       <c r="I363" s="2"/>
       <c r="J363" s="2"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -6414,7 +6635,7 @@
       <c r="I364" s="2"/>
       <c r="J364" s="2"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -6426,7 +6647,7 @@
       <c r="I365" s="2"/>
       <c r="J365" s="2"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -6438,7 +6659,7 @@
       <c r="I366" s="2"/>
       <c r="J366" s="2"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -6450,7 +6671,7 @@
       <c r="I367" s="2"/>
       <c r="J367" s="2"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -6462,7 +6683,7 @@
       <c r="I368" s="2"/>
       <c r="J368" s="2"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -6474,7 +6695,7 @@
       <c r="I369" s="2"/>
       <c r="J369" s="2"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -6486,7 +6707,7 @@
       <c r="I370" s="2"/>
       <c r="J370" s="2"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -6498,7 +6719,7 @@
       <c r="I371" s="2"/>
       <c r="J371" s="2"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -6510,7 +6731,7 @@
       <c r="I372" s="2"/>
       <c r="J372" s="2"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -6522,7 +6743,7 @@
       <c r="I373" s="2"/>
       <c r="J373" s="2"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -6534,7 +6755,7 @@
       <c r="I374" s="2"/>
       <c r="J374" s="2"/>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -6546,7 +6767,7 @@
       <c r="I375" s="2"/>
       <c r="J375" s="2"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -6558,7 +6779,7 @@
       <c r="I376" s="2"/>
       <c r="J376" s="2"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -6570,7 +6791,7 @@
       <c r="I377" s="2"/>
       <c r="J377" s="2"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -6582,7 +6803,7 @@
       <c r="I378" s="2"/>
       <c r="J378" s="2"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -6594,7 +6815,7 @@
       <c r="I379" s="2"/>
       <c r="J379" s="2"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -6606,7 +6827,7 @@
       <c r="I380" s="2"/>
       <c r="J380" s="2"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -6618,7 +6839,7 @@
       <c r="I381" s="2"/>
       <c r="J381" s="2"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -6630,7 +6851,7 @@
       <c r="I382" s="2"/>
       <c r="J382" s="2"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -6642,7 +6863,7 @@
       <c r="I383" s="2"/>
       <c r="J383" s="2"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -6654,7 +6875,7 @@
       <c r="I384" s="2"/>
       <c r="J384" s="2"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -6666,7 +6887,7 @@
       <c r="I385" s="2"/>
       <c r="J385" s="2"/>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -6678,7 +6899,7 @@
       <c r="I386" s="2"/>
       <c r="J386" s="2"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -6690,7 +6911,7 @@
       <c r="I387" s="2"/>
       <c r="J387" s="2"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -6702,7 +6923,7 @@
       <c r="I388" s="2"/>
       <c r="J388" s="2"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -6714,7 +6935,7 @@
       <c r="I389" s="2"/>
       <c r="J389" s="2"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -6726,7 +6947,7 @@
       <c r="I390" s="2"/>
       <c r="J390" s="2"/>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -6738,7 +6959,7 @@
       <c r="I391" s="2"/>
       <c r="J391" s="2"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -6750,7 +6971,7 @@
       <c r="I392" s="2"/>
       <c r="J392" s="2"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -6762,7 +6983,7 @@
       <c r="I393" s="2"/>
       <c r="J393" s="2"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -6774,7 +6995,7 @@
       <c r="I394" s="2"/>
       <c r="J394" s="2"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -6786,7 +7007,7 @@
       <c r="I395" s="2"/>
       <c r="J395" s="2"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -6798,7 +7019,7 @@
       <c r="I396" s="2"/>
       <c r="J396" s="2"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -6810,7 +7031,7 @@
       <c r="I397" s="2"/>
       <c r="J397" s="2"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -6822,7 +7043,7 @@
       <c r="I398" s="2"/>
       <c r="J398" s="2"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -6834,7 +7055,7 @@
       <c r="I399" s="2"/>
       <c r="J399" s="2"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -6846,7 +7067,7 @@
       <c r="I400" s="2"/>
       <c r="J400" s="2"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -6858,7 +7079,7 @@
       <c r="I401" s="2"/>
       <c r="J401" s="2"/>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -6870,7 +7091,7 @@
       <c r="I402" s="2"/>
       <c r="J402" s="2"/>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -6882,7 +7103,7 @@
       <c r="I403" s="2"/>
       <c r="J403" s="2"/>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -6894,7 +7115,7 @@
       <c r="I404" s="2"/>
       <c r="J404" s="2"/>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -6906,7 +7127,7 @@
       <c r="I405" s="2"/>
       <c r="J405" s="2"/>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -6918,7 +7139,7 @@
       <c r="I406" s="2"/>
       <c r="J406" s="2"/>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -6930,7 +7151,7 @@
       <c r="I407" s="2"/>
       <c r="J407" s="2"/>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -6942,7 +7163,7 @@
       <c r="I408" s="2"/>
       <c r="J408" s="2"/>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -6954,7 +7175,7 @@
       <c r="I409" s="2"/>
       <c r="J409" s="2"/>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -6966,7 +7187,7 @@
       <c r="I410" s="2"/>
       <c r="J410" s="2"/>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -6978,7 +7199,7 @@
       <c r="I411" s="2"/>
       <c r="J411" s="2"/>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -6990,7 +7211,7 @@
       <c r="I412" s="2"/>
       <c r="J412" s="2"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -7002,7 +7223,7 @@
       <c r="I413" s="2"/>
       <c r="J413" s="2"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -7014,7 +7235,7 @@
       <c r="I414" s="2"/>
       <c r="J414" s="2"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -7026,7 +7247,7 @@
       <c r="I415" s="2"/>
       <c r="J415" s="2"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -7038,7 +7259,7 @@
       <c r="I416" s="2"/>
       <c r="J416" s="2"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -7050,7 +7271,7 @@
       <c r="I417" s="2"/>
       <c r="J417" s="2"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -7062,7 +7283,7 @@
       <c r="I418" s="2"/>
       <c r="J418" s="2"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -7074,7 +7295,7 @@
       <c r="I419" s="2"/>
       <c r="J419" s="2"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -7086,7 +7307,7 @@
       <c r="I420" s="2"/>
       <c r="J420" s="2"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -7098,7 +7319,7 @@
       <c r="I421" s="2"/>
       <c r="J421" s="2"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -7110,7 +7331,7 @@
       <c r="I422" s="2"/>
       <c r="J422" s="2"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -7122,7 +7343,7 @@
       <c r="I423" s="2"/>
       <c r="J423" s="2"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -7134,7 +7355,7 @@
       <c r="I424" s="2"/>
       <c r="J424" s="2"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -7146,7 +7367,7 @@
       <c r="I425" s="2"/>
       <c r="J425" s="2"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -7158,7 +7379,7 @@
       <c r="I426" s="2"/>
       <c r="J426" s="2"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -7170,7 +7391,7 @@
       <c r="I427" s="2"/>
       <c r="J427" s="2"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -7182,7 +7403,7 @@
       <c r="I428" s="2"/>
       <c r="J428" s="2"/>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -7194,7 +7415,7 @@
       <c r="I429" s="2"/>
       <c r="J429" s="2"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -7206,7 +7427,7 @@
       <c r="I430" s="2"/>
       <c r="J430" s="2"/>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -7218,7 +7439,7 @@
       <c r="I431" s="2"/>
       <c r="J431" s="2"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -7230,7 +7451,7 @@
       <c r="I432" s="2"/>
       <c r="J432" s="2"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -7242,7 +7463,7 @@
       <c r="I433" s="2"/>
       <c r="J433" s="2"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -7254,7 +7475,7 @@
       <c r="I434" s="2"/>
       <c r="J434" s="2"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -7266,7 +7487,7 @@
       <c r="I435" s="2"/>
       <c r="J435" s="2"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -7278,7 +7499,7 @@
       <c r="I436" s="2"/>
       <c r="J436" s="2"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -7290,7 +7511,7 @@
       <c r="I437" s="2"/>
       <c r="J437" s="2"/>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -7302,7 +7523,7 @@
       <c r="I438" s="2"/>
       <c r="J438" s="2"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -7314,7 +7535,7 @@
       <c r="I439" s="2"/>
       <c r="J439" s="2"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -7326,7 +7547,7 @@
       <c r="I440" s="2"/>
       <c r="J440" s="2"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -7338,7 +7559,7 @@
       <c r="I441" s="2"/>
       <c r="J441" s="2"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -7350,7 +7571,7 @@
       <c r="I442" s="2"/>
       <c r="J442" s="2"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -7362,7 +7583,7 @@
       <c r="I443" s="2"/>
       <c r="J443" s="2"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -7374,7 +7595,7 @@
       <c r="I444" s="2"/>
       <c r="J444" s="2"/>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -7386,7 +7607,7 @@
       <c r="I445" s="2"/>
       <c r="J445" s="2"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -7398,7 +7619,7 @@
       <c r="I446" s="2"/>
       <c r="J446" s="2"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -7410,7 +7631,7 @@
       <c r="I447" s="2"/>
       <c r="J447" s="2"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -7422,7 +7643,7 @@
       <c r="I448" s="2"/>
       <c r="J448" s="2"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -7434,7 +7655,7 @@
       <c r="I449" s="2"/>
       <c r="J449" s="2"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -7446,7 +7667,7 @@
       <c r="I450" s="2"/>
       <c r="J450" s="2"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -7458,7 +7679,7 @@
       <c r="I451" s="2"/>
       <c r="J451" s="2"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -7470,7 +7691,7 @@
       <c r="I452" s="2"/>
       <c r="J452" s="2"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -7482,7 +7703,7 @@
       <c r="I453" s="2"/>
       <c r="J453" s="2"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -7494,7 +7715,7 @@
       <c r="I454" s="2"/>
       <c r="J454" s="2"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -7506,7 +7727,7 @@
       <c r="I455" s="2"/>
       <c r="J455" s="2"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -7518,7 +7739,7 @@
       <c r="I456" s="2"/>
       <c r="J456" s="2"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -7530,7 +7751,7 @@
       <c r="I457" s="2"/>
       <c r="J457" s="2"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -7542,7 +7763,7 @@
       <c r="I458" s="2"/>
       <c r="J458" s="2"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -7554,7 +7775,7 @@
       <c r="I459" s="2"/>
       <c r="J459" s="2"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -7566,7 +7787,7 @@
       <c r="I460" s="2"/>
       <c r="J460" s="2"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -7578,7 +7799,7 @@
       <c r="I461" s="2"/>
       <c r="J461" s="2"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -7590,7 +7811,7 @@
       <c r="I462" s="2"/>
       <c r="J462" s="2"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -7602,7 +7823,7 @@
       <c r="I463" s="2"/>
       <c r="J463" s="2"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -7614,7 +7835,7 @@
       <c r="I464" s="2"/>
       <c r="J464" s="2"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -7626,7 +7847,7 @@
       <c r="I465" s="2"/>
       <c r="J465" s="2"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -7638,7 +7859,7 @@
       <c r="I466" s="2"/>
       <c r="J466" s="2"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -7650,7 +7871,7 @@
       <c r="I467" s="2"/>
       <c r="J467" s="2"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -7662,7 +7883,7 @@
       <c r="I468" s="2"/>
       <c r="J468" s="2"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -7674,7 +7895,7 @@
       <c r="I469" s="2"/>
       <c r="J469" s="2"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -7686,7 +7907,7 @@
       <c r="I470" s="2"/>
       <c r="J470" s="2"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -7698,7 +7919,7 @@
       <c r="I471" s="2"/>
       <c r="J471" s="2"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -7710,7 +7931,7 @@
       <c r="I472" s="2"/>
       <c r="J472" s="2"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -7722,7 +7943,7 @@
       <c r="I473" s="2"/>
       <c r="J473" s="2"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -7734,7 +7955,7 @@
       <c r="I474" s="2"/>
       <c r="J474" s="2"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -7746,7 +7967,7 @@
       <c r="I475" s="2"/>
       <c r="J475" s="2"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -7758,7 +7979,7 @@
       <c r="I476" s="2"/>
       <c r="J476" s="2"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -7770,7 +7991,7 @@
       <c r="I477" s="2"/>
       <c r="J477" s="2"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -7782,7 +8003,7 @@
       <c r="I478" s="2"/>
       <c r="J478" s="2"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -7794,7 +8015,7 @@
       <c r="I479" s="2"/>
       <c r="J479" s="2"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -7806,7 +8027,7 @@
       <c r="I480" s="2"/>
       <c r="J480" s="2"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -7818,7 +8039,7 @@
       <c r="I481" s="2"/>
       <c r="J481" s="2"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -7830,7 +8051,7 @@
       <c r="I482" s="2"/>
       <c r="J482" s="2"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -7842,7 +8063,7 @@
       <c r="I483" s="2"/>
       <c r="J483" s="2"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -7854,7 +8075,7 @@
       <c r="I484" s="2"/>
       <c r="J484" s="2"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -7866,7 +8087,7 @@
       <c r="I485" s="2"/>
       <c r="J485" s="2"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -7878,7 +8099,7 @@
       <c r="I486" s="2"/>
       <c r="J486" s="2"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -7890,7 +8111,7 @@
       <c r="I487" s="2"/>
       <c r="J487" s="2"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -7902,7 +8123,7 @@
       <c r="I488" s="2"/>
       <c r="J488" s="2"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -7914,7 +8135,7 @@
       <c r="I489" s="2"/>
       <c r="J489" s="2"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -7926,7 +8147,7 @@
       <c r="I490" s="2"/>
       <c r="J490" s="2"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -7938,7 +8159,7 @@
       <c r="I491" s="2"/>
       <c r="J491" s="2"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -7950,7 +8171,7 @@
       <c r="I492" s="2"/>
       <c r="J492" s="2"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -7962,7 +8183,7 @@
       <c r="I493" s="2"/>
       <c r="J493" s="2"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -7974,7 +8195,7 @@
       <c r="I494" s="2"/>
       <c r="J494" s="2"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -7986,7 +8207,7 @@
       <c r="I495" s="2"/>
       <c r="J495" s="2"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -7998,7 +8219,7 @@
       <c r="I496" s="2"/>
       <c r="J496" s="2"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -8010,7 +8231,7 @@
       <c r="I497" s="2"/>
       <c r="J497" s="2"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -8022,7 +8243,7 @@
       <c r="I498" s="2"/>
       <c r="J498" s="2"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -8034,7 +8255,7 @@
       <c r="I499" s="2"/>
       <c r="J499" s="2"/>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -8056,6 +8277,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -8080,7 +8302,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -8094,810 +8316,810 @@
     <col min="10" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="406" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J3" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="360" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J5" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="406" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J6" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="360" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="406" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="J9" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="232" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J11" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="J13" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="J14" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="H15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="J15" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="232" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="216" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="J17" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="F18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J18" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J19" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="216" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="B21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="J21" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H21" s="4" t="s">
+    <row r="23" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="J23" s="4" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="H22" s="4" t="s">
+    <row r="24" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="4" t="s">
+      <c r="J24" s="4" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="4" t="s">
+    <row r="25" spans="1:10" ht="116" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="J26" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -8909,241 +9131,241 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
       <c r="B2" s="10"/>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B6" s="10"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="10"/>
     </row>
-    <row r="18" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B18" s="10" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="10"/>
     </row>
-    <row r="21" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="10"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="10" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="10" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="10" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="10" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="10"/>
     </row>
-    <row r="29" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="10"/>
     </row>
-    <row r="32" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>173</v>
-      </c>
       <c r="B33" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -9154,448 +9376,448 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>177</v>
-      </c>
       <c r="H1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
       <c r="D2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" t="s">
         <v>178</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>179</v>
       </c>
-      <c r="F2" t="s">
-        <v>180</v>
-      </c>
       <c r="H2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>184</v>
       </c>
-      <c r="H3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F4" t="s">
-        <v>220</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" t="s">
         <v>195</v>
       </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="F7" t="s">
         <v>212</v>
       </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F8" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B10">
         <v>38698</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F10" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" t="s">
         <v>224</v>
       </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E11" t="s">
-        <v>179</v>
-      </c>
-      <c r="F11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" t="s">
         <v>206</v>
       </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E12" t="s">
-        <v>179</v>
-      </c>
-      <c r="F12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B13">
         <v>38702</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E13" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>265</v>
-      </c>
-      <c r="E13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>231</v>
-      </c>
-      <c r="E14" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>236</v>
-      </c>
-      <c r="E15" t="s">
-        <v>179</v>
-      </c>
-      <c r="F15" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>267</v>
       </c>
       <c r="B16">
         <v>38705</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>268</v>
-      </c>
-      <c r="E16" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>270</v>
       </c>
       <c r="B17">
         <v>38706</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>271</v>
-      </c>
-      <c r="E17" t="s">
-        <v>179</v>
-      </c>
-      <c r="F17" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>273</v>
       </c>
       <c r="B18">
         <v>38707</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>274</v>
-      </c>
-      <c r="E18" t="s">
-        <v>179</v>
-      </c>
-      <c r="F18" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>276</v>
       </c>
       <c r="B19">
         <v>38708</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
+        <v>275</v>
+      </c>
+      <c r="E19" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>277</v>
-      </c>
-      <c r="E19" t="s">
-        <v>179</v>
-      </c>
-      <c r="F19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>279</v>
       </c>
       <c r="B20">
         <v>38709</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
+        <v>278</v>
+      </c>
+      <c r="E20" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" t="s">
         <v>280</v>
       </c>
-      <c r="E20" t="s">
-        <v>281</v>
-      </c>
-      <c r="F20" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+  <sortState ref="A2:F21">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/control/Control_Ejecucion.xlsx
+++ b/control/Control_Ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GreenSQA\AppData\Local\Temp\claude\c--ATM-AppMovil-MiBanco\4bd799e8-9fec-418b-87c7-f5e93e1a90ec\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4013C14B-A490-4038-BF0F-EE797F1F5911}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4F6607-86F2-4A1B-AA58-74CED9A8F86B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="453">
   <si>
     <t>Caso</t>
   </si>
@@ -892,9 +892,6 @@
     <t>TipoDocumento (CC)</t>
   </si>
   <si>
-    <t>NumDocumento: AUTO o vacio toma un CC DISPONIBLE del listado; si la app indica que ya esta registrado lo descarta y toma otro (max 3). Clave: vacia = se genera segun RN-R07; si se informa debe cumplir RN-R07. OTP: vacio = 000000.</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
@@ -913,9 +910,6 @@
     <t>@38519</t>
   </si>
   <si>
-    <t>NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume. Con documento informado, Clave vacia = la del listado; si se informa, 4 digitos.</t>
-  </si>
-  <si>
     <t>LOG-001</t>
   </si>
   <si>
@@ -1111,9 +1105,6 @@
     <t>@38529</t>
   </si>
   <si>
-    <t>NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS). Clave = la nueva: vacia se genera segun RN-R07 y distinta de la actual; si se informa debe cumplir RN-R07. OTP: vacio = 000000. Cambia la clave del cliente: el listado guarda la nueva al confirmar; si falla tras enviar el cambio queda FALLIDO.</t>
-  </si>
-  <si>
     <t>@38526</t>
   </si>
   <si>
@@ -1195,9 +1186,6 @@
     <t>TipoDocumento (CC), TipoProducto, Monto</t>
   </si>
   <si>
-    <t>Compara el Monto (saldo esperado segun el backend, p. ej. 22746864.51) con el de las tarjetas del TipoProducto indicado y valida la tarjeta como en su caso. Una fila por producto a comparar. Monto y TipoProducto son obligatorios.</t>
-  </si>
-  <si>
     <t>PROD-AHO-001</t>
   </si>
   <si>
@@ -1334,6 +1322,481 @@
   </si>
   <si>
     <t>2658679.07</t>
+  </si>
+  <si>
+    <t>39561</t>
+  </si>
+  <si>
+    <t>Cuentas</t>
+  </si>
+  <si>
+    <t>Carga exitosa del home muestra Productos del cliente: cuenta  ahorro</t>
+  </si>
+  <si>
+    <t>1.el sistema muestra la pantalla de bienvenida y el formulario de inicio de sesión.
+2.El usuario es autenticado con éxito y se inicia la sesión.
+3.Se carga la interfaz principal mostrando el saludo "Hola [Nombre]", los accesos rápidos y los módulos financieros.
+4. Al verificar que la  la sesion de  " tus cuentas" se  muestra  La tarjeta muestra la siguiente información exacta según el diseño base:El tipo de cuenta y los últimos 4 dígitos enmascarados ("Cuenta de ahorros **** 5038").
+5 La etiqueta o tag de categoría (eje: "Ahorro con propósito") dentro de su contenedor gris.
+6.El saldo formateado correctamente con signo de moneda, separador de miles y decimales ("$ 26,000,000,00").
+7.El icono de visibilidad/ojo tachado en la esquina superior derecha de la tarjeta.</t>
+  </si>
+  <si>
+    <t>39562</t>
+  </si>
+  <si>
+    <t>1.el sistema muestra la pantalla de bienvenida y el formulario de inicio de sesión.
+2.El usuario es autenticado con éxito y se inicia la sesión.
+3.Se carga la interfaz principal mostrando el saludo "Hola [Nombre]", los accesos rápidos y los módulos financieros.
+4.Al verificar que la  la sesion de  " tus cuentas" se  muestra  La tarjeta muestra la siguiente información exacta según el diseño base: El tipo de cuenta y los últimos 4 dígitos enmascarados ("Cuenta Corriente **** 5038").
+5.La etiqueta o tag de categoría (eje "Cuenta corriente PN") dentro de su contenedor gris.El saldo formateado correctamente con signo de moneda, separador de miles y decimales ("$ 26,000,000,00").El icono de visibilidad/ojo tachado en la esquina superior derecha de la tarjeta.</t>
+  </si>
+  <si>
+    <t>39563</t>
+  </si>
+  <si>
+    <t>1.el sistema muestra la pantalla de bienvenida y el formulario de inicio de sesión.
+2.El usuario es autenticado con éxito y se inicia la sesión.
+3.Se carga la interfaz principal mostrando el saludo "Hola [Nombre]", los accesos rápidos y los módulos financieros.
+4.Cada tarjeta de Libre Inversión muestra de manera correcta:El título del producto ("Crédito") y el saldo adeudado formateado con signo de pesos, separador de miles y decimales ($ 18,000,000,00).
+5.El indicador visual dinámico según el estado de la cuota:Caso Vencido: Punto rojo y texto "Cuota venció Hoy".
+6.Caso Vigente: Punto verde y texto "Cuota vence 24 Oct".Un botón o icono de flecha hacia la derecha &gt; que indica navegabilidad.</t>
+  </si>
+  <si>
+    <t>39564</t>
+  </si>
+  <si>
+    <t>39565</t>
+  </si>
+  <si>
+    <t>39566</t>
+  </si>
+  <si>
+    <t>Visualización detalle de Cuentas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripción: Detalle Cuentas
+Precondiciones: Se abre el detalle de la cuenta seleccionada y muestra los datos de la cuenta
+1.Iniciar sesión de forma correcta, ubicarse en el Home y localizar la sección de "Tus cuentas".
+2.Hacer clic sobre la tarjeta de la cuenta de ahorros seleccionada.
+3.Verificar la sección superior de la cabecera e información general de la cuenta.
+4.Validar la barra de acciones rápidas del producto.
+5. Inspeccionar el bloque inferior correspondiente a "Movimientos".
+</t>
+  </si>
+  <si>
+    <t>1.Se visualiza la tarjeta de la cuenta de ahorros activa con los datos enmascarados ("Cuenta ahorros **** 5038") y su saldo.
+2.El sistema procesa la solicitud (ID 10 / ID 11 según el tipo) y redirige correctamente al usuario hacia la pantalla de "Detalle de Cuenta".
+3. Se muestran correctamente los siguientes datos del producto:
+*Tipo y nombre de la cuenta junto al número de cuenta completo, visible
+*Opción o botón para "Compartir" datos de la cuenta en la esquina superior derecha.
+*El bloque de "Saldo disponible" con su cifra formateada de forma destacada ($ 26,000,000,00).
+*El desglose de "Saldo en canje".
+4.Se muestra el texto informativo: "Los movimientos listados corresponden a las últimas 20 transacciones realizadas en su producto".
+6.Se despliega el listado de transacciones recientes, donde cada registro incluye de forma clara: Tipo de transacción (ej. Trf ext 0021430), Fecha y hora exacta (ej. 05 May 2026 - 12:30 pm), el monto correspondiente con su formato monetario ($ 3,700,000,00) y un icono de navegación &gt; para ver el detalle de cada movimiento.</t>
+  </si>
+  <si>
+    <t>39567</t>
+  </si>
+  <si>
+    <t>Detalle de cuenta muestra máximo 20 movimientos</t>
+  </si>
+  <si>
+    <t>Descripción: Detalle Cuentas
+Precondiciones: Clientes con más de 20 transacciones solo ven las 20 más recientes
+1.Iniciar sesión en la aplicación móvil utilizando un usuario de prueba que registre un historial alto (por ejemplo, 30 o más transacciones) en el backend para el mes actual.
+2. Seleccionar la tarjeta de la cuenta bajo prueba en la sección "Tus cuentas" para abrir la pantalla de "Detalle de Cuenta".
+3. Verificar la presencia y legibilidad del texto informativo o descriptivo ubicado arriba del listado de transacciones.
+4.Realizar scroll hacia abajo en la pantalla y contar exhaustivamente el número total de registros de transacciones renderizados en la lista.
+Comparar las fechas y horas de las primeras y últimas transacciones de la lista con los datos reales del backend del usuario.</t>
+  </si>
+  <si>
+    <t>1.El ingreso a la aplicación es exitoso y se despliega la pantalla principal (Home).
+2.Se carga la vista detallada mostrando los saldos y el bloque inferior de "Movimientos".
+3.Se visualiza explícitamente el mensaje de advertencia al cliente: "Los movimientos listados corresponden a las últimas 20 transacciones realizadas en su producto".
+4.El listado se corta de manera estricta al llegar al registro número 20. 
+5.El sistema no permite cargar ni visualizar transacciones adicionales más allá de este límite en esta vista.
+6.Los movimientos se muestran ordenados cronológicamente de forma descendente (de la más nueva a la más antigua), confirmando que las 20 transacciones visibles corresponden exactamente a las 20 más recientes.</t>
+  </si>
+  <si>
+    <t>39568</t>
+  </si>
+  <si>
+    <t>Detalle de cuenta muestra movimientos en el rango hoy − 1 mes</t>
+  </si>
+  <si>
+    <t>Descripción: Detalle Cuentas
+Precondiciones: Clientes solo visualizan los movimiento de los útlimos 30 días
+1. Iniciar sesión con un usuario que registre transacciones antiguas (ej. de hace 45 o 60 días) y transacciones recientes (dentro de los últimos 30 días).
+2.Seleccionar la cuenta en la sección "Tus cuentas" para acceder a la pantalla de "Detalle de Cuenta".
+3.Inspeccionar las fechas de todo el listado de transacciones renderizado en pantalla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Ingreso exitoso a la aplicación.
+2.Carga la sección de "Movimientos".
+3.El sistema aplica el filtro temporal correctamente. Únicamente se listan los movimientos cuyo rango de fecha se encuentre entre la fecha de Hoy y los últimos 30 días. 
+4.Cualquier transacción más antigua queda excluida visualmente.
+</t>
+  </si>
+  <si>
+    <t>39569</t>
+  </si>
+  <si>
+    <t>No hay botón "Ver más" ni carga adicional en el listado del Home</t>
+  </si>
+  <si>
+    <t>Descripción: No existe opción de paginación, solo scroll natural para mostrar los 20 movimientos
+Precondiciones: El usuario ha iniciado sesión y se encuentra en el Home.
+La cuenta del cliente tiene exactamente 20 o más movimientos registrados.
+1.Cargar la pantalla principal (Home) de la aplicación.
+2.Revisar la parte inferior del listado inicial de movimientos.
+3.Desplazar la pantalla hacia abajo utilizando el scroll natural.
+4.Verificar el final del contenedor del listado</t>
+  </si>
+  <si>
+    <t>1.No existe ningún control ni botones de paginación numérica.
+2.No se visualiza un botón con el texto "Ver más".
+3.La pantalla permite un desplazamiento fluido (scroll natural) para mostrar la totalidad de los 20 movimientos.
+4.No se realiza ninguna petición de carga adicional de elementos al llegar al final.</t>
+  </si>
+  <si>
+    <t>39570</t>
+  </si>
+  <si>
+    <t>No existe opción de paginación ni scroll infinito para más movimientos</t>
+  </si>
+  <si>
+    <t>Descripción: Detalle Cuentas
+Precondiciones: No hay botón "Ver más" ni carga adicional en el listado del Home
+1.Iniciar sesión e ingresar a la pantalla de "Detalle de Cuenta" de un producto con alto volumen transaccional.
+2.Desplazarse (hacer scrolldown) hasta llegar al último registro visible de la lista (movimiento número 20).
+3.Forzar el gesto de scroll hacia abajo en el extremo inferior del listado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Se muestra el bloque inferior con la lista inicial de movimientos.
+2.Al llegar al final de la lista, no aparece ningún botón que diga "Ver más", "Cargar más" ni indicadores de paginación (1, 2, 3...).
+3.La aplicación no realiza peticiones adicionales al backend (lazy loading) ni activa un scroll infinito. 
+4.La lista permanece fija con el tope de elementos renderizados.
+</t>
+  </si>
+  <si>
+    <t>39571</t>
+  </si>
+  <si>
+    <t>Detalles de la transacción muestra monto, movimientos</t>
+  </si>
+  <si>
+    <t>Descripción: Detalle de transacciones
+Precondiciones: Se abre el detalle de la transacción seleccionada y muestra los datos de la cuenta y últimos movimientos realizados
+1. En la pantalla de "Detalle de Cuenta", ubicar la lista de movimientos recientes.
+2. Hacer clic sobre cualquiera de las transacciones (ej. Trf ext 0021430).
+3. Verificar la información y datos enmascarados mostrados en el comprobante.</t>
+  </si>
+  <si>
+    <t>1.Se listan las transacciones con su flecha de navegación &gt;.
+2.Se abre correctamente la pantalla flotante o modal de "Detalle de Transacción".
+3.La pantalla refleja de manera exacta los datos del movimiento seleccionado: Monto formateado con decimales, nombre/tipo de transacción, cuenta de origen, cuenta de destino (si aplica), fecha, hora y número de referencia.</t>
+  </si>
+  <si>
+    <t>39572</t>
+  </si>
+  <si>
+    <t>Descargar comprobante de transacción</t>
+  </si>
+  <si>
+    <t>Descripción: Detalle de transacciones
+Precondiciones: Se genera imagen en el front con los detalles de la transacción y permite descargarla
+1.Acceder al "Detalle de una Transacción" específica.
+2. Presionar el botón de acción "Descargar" (o icono correspondiente).
+3.Confirmar la descarga y dirigirse a la galería o carpeta de archivos locales del dispositivo.</t>
+  </si>
+  <si>
+    <t>1.Se despliega el comprobante con los datos completos del movimiento.
+2.El frontend genera/renderiza exitosamente una imagen limpia de la transacción. El sistema solicita permisos de almacenamiento si es la primera vez.
+3.Se valida que la imagen del comprobante se guardó correctamente, con buena resolución y con los textos legibles.</t>
+  </si>
+  <si>
+    <t>39573</t>
+  </si>
+  <si>
+    <t>Compartir comprobante de transacción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripción: Detalle de transacciones
+Precondiciones: Se genera imagen en el front con los detalles de la transacción y permite compartirla
+1. Ingresar al "Detalle de una Transacción" específica.
+2.Presionar el botón o icono de "Compartir" (generalmente ubicado en la parte inferior o esquina superior).
+3.Seleccionar una aplicación externa (ej. WhatsApp, Correo, Mensajes) para enviar el elemento.
+</t>
+  </si>
+  <si>
+    <t>1.Se visualiza el resumen de la transacción en pantalla.
+2.El sistema procesa la imagen en el frontend y despliega de manera inmediata la sábana o menú nativo de compartir del celular.
+3. La imagen del comprobante se adjunta de forma automática en la app externa seleccionada y se envía de forma correcta al destinatario sin corromperse.</t>
+  </si>
+  <si>
+    <t>NumDocumento: AUTO o vacio toma un CC DISPONIBLE del listado; si la app indica que ya esta registrado lo descarta y toma otro (max 3). Clave: con AUTO, vacia = se genera segun RN-R07; con documento informado es obligatoria. Si se informa debe cumplir RN-R07. OTP: vacio = 000000.</t>
+  </si>
+  <si>
+    <t>NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume y la Clave va vacia. Con documento informado la Clave es obligatoria (4 digitos).</t>
+  </si>
+  <si>
+    <t>NumDocumento: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS). Clave = la nueva: con AUTO, vacia se genera segun RN-R07 y distinta de la actual; con documento informado es obligatoria. Si se informa debe cumplir RN-R07. OTP: vacio = 000000. Cambia la clave del cliente: el listado guarda la nueva al confirmar; si falla tras enviar el cambio queda FALLIDO.</t>
+  </si>
+  <si>
+    <t>Compara el Monto (saldo esperado segun el backend, p. ej. 22746864.51) con el de las tarjetas del TipoProducto indicado y valida solo el formato del saldo (la informacion de cada tarjeta es de 38705 a 38708). Una fila por producto a comparar. Monto y TipoProducto son obligatorios.</t>
+  </si>
+  <si>
+    <t>39561 - Producto cuenta de ahorro en el Home (Cuentas)</t>
+  </si>
+  <si>
+    <t>@39561</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38705 (repite su texto). Como 38702 con AHORRO. Valida el titulo Cuentas de ahorro **** 1234, la etiqueta, el saldo con formato $22.746.864,51 y el icono de ocultar montos. Monto opcional: si se informa, se compara con el saldo.</t>
+  </si>
+  <si>
+    <t>39562 - Producto cuenta corriente en el Home (Cuentas)</t>
+  </si>
+  <si>
+    <t>@39562</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38706 (repite su texto). Como 38705 con CORRIENTE. Hoy ningun cliente revisado tiene cuenta corriente: solicitar datos o informar el documento.</t>
+  </si>
+  <si>
+    <t>39563 - Producto credito de libre inversion (Prestamos) en el Home (Cuentas)</t>
+  </si>
+  <si>
+    <t>@39563</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38707 (repite su texto). Como 38702 con PRESTAMO (la app muestra estos creditos como Prestamos). Valida titulo, saldo con formato, estado de la cuota (Cuota vencio 1 Jun) y que la tarjeta se pueda abrir. Monto opcional.</t>
+  </si>
+  <si>
+    <t>39564 - Producto credito rotativo en el Home (Cuentas)</t>
+  </si>
+  <si>
+    <t>@39564</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38708 (repite su texto). Como 38702 con ROTATIVO. Valida Credito Rotativo con la etiqueta Cupo aprobado, el monto con formato y que la tarjeta se pueda abrir. Monto opcional.</t>
+  </si>
+  <si>
+    <t>39565 - Saldos de los productos en el Home (Cuentas)</t>
+  </si>
+  <si>
+    <t>@39565</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38709 (repite su texto). Compara el Monto (saldo esperado segun el backend, p. ej. 22746864.51) con el de las tarjetas del TipoProducto indicado y valida solo el formato del saldo (la informacion de cada tarjeta es de 38705 a 38708). Una fila por producto a comparar. Monto y TipoProducto son obligatorios.</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Mismo escenario de productos del Home (38705); repite el texto de 38705</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Mismo escenario de productos del Home (38705); repite el texto de 38706</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Mismo escenario de productos del Home (38705); repite el texto de 38707</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Mismo escenario de productos del Home (38705); repite el texto de 38708</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control. Mismo escenario de productos del Home (38705); repite el texto de 38709</t>
+  </si>
+  <si>
+    <t>39566 - Detalle de cuenta de ahorros</t>
+  </si>
+  <si>
+    <t>@39566</t>
+  </si>
+  <si>
+    <t>Como 38519: AUTO toma un cliente REGISTRADO con clave que muestre la cuenta de ahorros (columna PRODUCTOS_HOME del listado), revisando hasta 3 clientes. Abre el detalle de la cuenta y valida tipo y numero completo, el boton para compartir, saldo disponible y saldo en canje con formato, las acciones rapidas y la seccion Movimientos (lista o aviso de que no hay movimientos en los ultimos 30 dias). TipoProducto y Monto no aplican. Vuelve al Home y cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-DET-001). Movimientos: acepta la lista o el aviso sin movimientos (ningun cliente de prueba tiene movimientos al 15/10)</t>
+  </si>
+  <si>
+    <t>CTA-DET-001</t>
+  </si>
+  <si>
+    <t>Detalle de la cuenta de ahorros</t>
+  </si>
+  <si>
+    <t>SALDO-003</t>
+  </si>
+  <si>
+    <t>REC-OTP-002</t>
+  </si>
+  <si>
+    <t>SKEL-002</t>
+  </si>
+  <si>
+    <t>HOME-003</t>
+  </si>
+  <si>
+    <t>CTA-AHO-001</t>
+  </si>
+  <si>
+    <t>Cuenta de ahorro en el Home (repite 38705)</t>
+  </si>
+  <si>
+    <t>CTA-PRE-001</t>
+  </si>
+  <si>
+    <t>Prestamos en el Home (repite 38707)</t>
+  </si>
+  <si>
+    <t>CTA-ROT-001</t>
+  </si>
+  <si>
+    <t>Credito rotativo en el Home (repite 38708)</t>
+  </si>
+  <si>
+    <t>38710 - Banner Exclusivo para ti del Home</t>
+  </si>
+  <si>
+    <t>@38710</t>
+  </si>
+  <si>
+    <t>Como 38519: AUTO o vacio toma un cliente REGISTRADO con clave del listado; no lo consume. Valida la seccion Exclusivo para ti con el banner de campanas y, si hay mas de una, que al deslizar muestre la siguiente (con una sola campana queda como observacion). Cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (HOME-BAN-001). Con una sola campana, el deslizamiento queda como observacion</t>
+  </si>
+  <si>
+    <t>HOME-BAN-001</t>
+  </si>
+  <si>
+    <t>Banner Exclusivo para ti</t>
+  </si>
+  <si>
+    <t>39571 - Detalle de una transaccion de la cuenta</t>
+  </si>
+  <si>
+    <t>@39571</t>
+  </si>
+  <si>
+    <t>Como 39566 (cliente con cuenta de ahorros). Abre el movimiento mas reciente y valida monto, fecha y hora iguales a la lista, numero de comprobante y descripcion. Requiere un cliente con movimientos: informe NumDocumento y Clave; con AUTO los clientes del listado no tienen movimientos (Dato no apto). La cuenta de origen y destino no se muestran y el comprobante en ceros quedan como observacion. Vuelve al Home y cierra sesion al terminar.</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-TRX-001). Requiere un cliente con movimientos. Sin cuenta de origen ni destino en la app: observacion</t>
+  </si>
+  <si>
+    <t>CTA-TRX-001</t>
+  </si>
+  <si>
+    <t>Detalle de una transaccion (requiere cliente con movimientos)</t>
+  </si>
+  <si>
+    <t>39572 - Descargar comprobante de una transaccion</t>
+  </si>
+  <si>
+    <t>@39572</t>
+  </si>
+  <si>
+    <t>Como 39571 (requiere un cliente con movimientos: informe NumDocumento y Clave). Descarga el comprobante del movimiento mas reciente, valida el aviso de descarga y que la imagen quede guardada en el dispositivo (Documents/comprobante-N.png); la imagen se adjunta a la evidencia y se borra del dispositivo. La legibilidad la revisa una persona.</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-DES-001). Requiere un cliente con movimientos. La imagen se adjunta a la evidencia y se borra del dispositivo</t>
+  </si>
+  <si>
+    <t>CTA-DES-001</t>
+  </si>
+  <si>
+    <t>Descargar comprobante (requiere cliente con movimientos)</t>
+  </si>
+  <si>
+    <t>39573 - Compartir comprobante de una transaccion</t>
+  </si>
+  <si>
+    <t>@39573</t>
+  </si>
+  <si>
+    <t>Como 39571 (requiere un cliente con movimientos: informe NumDocumento y Clave). Abre el menu de compartir del dispositivo con la imagen del comprobante y lo cierra sin elegir app (no se envia nada). El video se detiene antes de abrir el menu y del menu solo se guarda su encabezado y vista previa (muestra contactos del dispositivo).</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-COM-001). Requiere un cliente con movimientos. El envio por una app externa queda manual</t>
+  </si>
+  <si>
+    <t>CTA-COM-001</t>
+  </si>
+  <si>
+    <t>Compartir comprobante (requiere cliente con movimientos)</t>
+  </si>
+  <si>
+    <t>39567 - Detalle de cuenta muestra maximo 20 movimientos</t>
+  </si>
+  <si>
+    <t>@39567</t>
+  </si>
+  <si>
+    <t>Mismo escenario que 39569 y 39570. Recorre la lista de movimientos: aviso de las ultimas 20 transacciones, maximo 20 ordenados del mas reciente al mas antiguo, formato de cada registro, sin Ver mas ni paginacion y sin carga adicional al forzar el final. Con menos de 20 movimientos el corte queda como observacion. Requiere un cliente con movimientos: informe NumDocumento y Clave (con AUTO los clientes del listado no tienen movimientos).</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-MOV-001). Mismo escenario que 39569 y 39570. Con menos de 20 movimientos el corte en 20 queda como observacion</t>
+  </si>
+  <si>
+    <t>CTA-MOV-001</t>
+  </si>
+  <si>
+    <t>Movimientos: maximo 20, orden y sin paginacion</t>
+  </si>
+  <si>
+    <t>39569 - Sin boton Ver mas ni carga adicional de movimientos</t>
+  </si>
+  <si>
+    <t>@39569</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 39567. El titulo dice listado del Home, pero el Home no muestra movimientos: se valida en el detalle de cuenta. Requiere un cliente con movimientos: informe NumDocumento y Clave (con AUTO los clientes del listado no tienen movimientos).</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-MOV-002). Mismo escenario de 39567; se valida en el detalle de cuenta (pendiente confirmar el titulo)</t>
+  </si>
+  <si>
+    <t>CTA-MOV-002</t>
+  </si>
+  <si>
+    <t>Sin Ver mas (mismo escenario de 39567)</t>
+  </si>
+  <si>
+    <t>39570 - Sin paginacion ni scroll infinito de movimientos</t>
+  </si>
+  <si>
+    <t>@39570</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 39567. La ausencia de peticiones de red queda manual. Requiere un cliente con movimientos: informe NumDocumento y Clave (con AUTO los clientes del listado no tienen movimientos).</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-MOV-003). Mismo escenario de 39567; la ausencia de peticiones de red queda manual</t>
+  </si>
+  <si>
+    <t>CTA-MOV-003</t>
+  </si>
+  <si>
+    <t>Sin paginacion (mismo escenario de 39567)</t>
+  </si>
+  <si>
+    <t>39568 - Detalle de cuenta muestra movimientos del ultimo mes</t>
+  </si>
+  <si>
+    <t>@39568</t>
+  </si>
+  <si>
+    <t>Recorre la lista de movimientos y valida que todas las fechas esten entre hoy menos un mes y hoy. Sin movimientos mas antiguos, la exclusion de los anteriores queda como observacion. Requiere un cliente con movimientos: informe NumDocumento y Clave (con AUTO los clientes del listado no tienen movimientos).</t>
+  </si>
+  <si>
+    <t>Disponible en la hoja Control (CTA-MOV-004). La exclusion de movimientos mas antiguos requiere un cliente que los tenga</t>
+  </si>
+  <si>
+    <t>CTA-MOV-004</t>
+  </si>
+  <si>
+    <t>Movimientos del ultimo mes</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1458,6 +1921,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1796,10 +2262,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -1813,7 +2279,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
@@ -1831,13 +2297,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -1861,7 +2327,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -1879,13 +2345,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -1898,21 +2364,21 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
@@ -1922,18 +2388,18 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
@@ -1946,21 +2412,21 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
@@ -1970,18 +2436,18 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -1994,21 +2460,21 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -2018,18 +2484,18 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
@@ -2042,18 +2508,18 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
@@ -2066,18 +2532,18 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
@@ -2090,18 +2556,18 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -2114,18 +2580,18 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -2138,18 +2604,18 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -2162,18 +2628,18 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -2184,22 +2650,22 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -2210,22 +2676,22 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -2236,22 +2702,22 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -2262,22 +2728,22 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -2288,24 +2754,24 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -2316,24 +2782,24 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -2344,24 +2810,24 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>305</v>
+        <v>395</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -2372,13 +2838,13 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I24" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
@@ -2386,10 +2852,10 @@
         <v>8</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -2405,13 +2871,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -2430,10 +2896,10 @@
         <v>8</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -2449,13 +2915,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -2471,13 +2937,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>189</v>
+        <v>396</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -2493,13 +2959,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -2515,13 +2981,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -2537,13 +3003,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>225</v>
+        <v>398</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -2559,13 +3025,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -2581,13 +3047,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
@@ -2603,13 +3069,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
@@ -2625,13 +3091,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -2647,13 +3113,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -2669,13 +3135,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -2691,13 +3157,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -2713,13 +3179,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
@@ -2730,22 +3196,22 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -2760,148 +3226,292 @@
       <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="A42" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+      <c r="J42" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
+      <c r="J44" s="2" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
+      <c r="J45" s="2" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
+      <c r="J46" s="2" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
+      <c r="J47" s="2" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
+      <c r="J48" s="2" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
+      <c r="J49" s="2" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
+      <c r="J50" s="2" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
+      <c r="J51" s="2" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
+      <c r="J52" s="2" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
+      <c r="J53" s="2" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
@@ -8287,9 +8897,9 @@
           </x14:formula1>
           <xm:sqref>H2:H500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{D83E1DC8-A2D6-4C03-80A4-D9E29D4F690D}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{ADF90D24-994E-4A2F-A10B-81ED9C0DAF51}">
           <x14:formula1>
-            <xm:f>Catalogo!$A$2:$A$21</xm:f>
+            <xm:f>Catalogo!$A$2:$A$35</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A500</xm:sqref>
         </x14:dataValidation>
@@ -8301,7 +8911,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8407,7 +9017,7 @@
         <v>35</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
@@ -8467,7 +9077,7 @@
         <v>35</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="406" x14ac:dyDescent="0.35">
@@ -8497,7 +9107,7 @@
         <v>35</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
@@ -8591,7 +9201,7 @@
         <v>35</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="203" x14ac:dyDescent="0.35">
@@ -8651,7 +9261,7 @@
         <v>35</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="203" x14ac:dyDescent="0.35">
@@ -8683,7 +9293,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
@@ -8715,7 +9325,7 @@
         <v>35</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="145" x14ac:dyDescent="0.35">
@@ -8747,7 +9357,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="174" x14ac:dyDescent="0.35">
@@ -8779,7 +9389,7 @@
         <v>35</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="232" x14ac:dyDescent="0.35">
@@ -8839,7 +9449,7 @@
         <v>35</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="145" x14ac:dyDescent="0.35">
@@ -8869,7 +9479,7 @@
         <v>35</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="145" x14ac:dyDescent="0.35">
@@ -8899,7 +9509,7 @@
         <v>35</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
@@ -8931,7 +9541,7 @@
         <v>35</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="203" x14ac:dyDescent="0.35">
@@ -8963,7 +9573,7 @@
         <v>35</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="174" x14ac:dyDescent="0.35">
@@ -8995,7 +9605,7 @@
         <v>35</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
@@ -9027,7 +9637,7 @@
         <v>35</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
@@ -9059,7 +9669,7 @@
         <v>35</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="116" x14ac:dyDescent="0.35">
@@ -9086,9 +9696,11 @@
         <v>34</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J25" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
@@ -9119,7 +9731,345 @@
         <v>35</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A28" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A29" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="203" x14ac:dyDescent="0.35">
+      <c r="A33" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A35" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="116" x14ac:dyDescent="0.35">
+      <c r="A37" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="116" x14ac:dyDescent="0.35">
+      <c r="A38" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -9209,7 +10159,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
@@ -9217,7 +10167,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -9230,18 +10180,18 @@
     </row>
     <row r="14" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -9337,7 +10287,7 @@
         <v>168</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -9357,7 +10307,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
@@ -9365,7 +10315,7 @@
         <v>172</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -9375,7 +10325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -9398,7 +10348,7 @@
         <v>176</v>
       </c>
       <c r="H1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -9418,15 +10368,15 @@
         <v>178</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>365</v>
       </c>
       <c r="H2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -9435,21 +10385,21 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
         <v>178</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -9458,21 +10408,21 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -9481,21 +10431,21 @@
         <v>28</v>
       </c>
       <c r="D5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
         <v>194</v>
       </c>
-      <c r="E5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F5" t="s">
-        <v>196</v>
-      </c>
       <c r="H5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -9504,21 +10454,21 @@
         <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
         <v>178</v>
       </c>
       <c r="F6" t="s">
-        <v>186</v>
+        <v>366</v>
       </c>
       <c r="H6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -9527,18 +10477,18 @@
         <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -9547,18 +10497,18 @@
         <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E8" t="s">
         <v>178</v>
       </c>
       <c r="F8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s">
         <v>76</v>
@@ -9567,18 +10517,18 @@
         <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
         <v>178</v>
       </c>
       <c r="F9" t="s">
-        <v>252</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B10">
         <v>38698</v>
@@ -9587,18 +10537,18 @@
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E10" t="s">
         <v>178</v>
       </c>
       <c r="F10" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
         <v>86</v>
@@ -9607,18 +10557,18 @@
         <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E11" t="s">
         <v>178</v>
       </c>
       <c r="F11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B12" t="s">
         <v>91</v>
@@ -9627,18 +10577,18 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
         <v>178</v>
       </c>
       <c r="F12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B13">
         <v>38702</v>
@@ -9647,18 +10597,18 @@
         <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E13" t="s">
         <v>178</v>
       </c>
       <c r="F13" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B14" t="s">
         <v>103</v>
@@ -9667,18 +10617,18 @@
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E14" t="s">
         <v>178</v>
       </c>
       <c r="F14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
         <v>107</v>
@@ -9687,18 +10637,18 @@
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E15" t="s">
         <v>178</v>
       </c>
       <c r="F15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B16">
         <v>38705</v>
@@ -9707,18 +10657,18 @@
         <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E16" t="s">
         <v>178</v>
       </c>
       <c r="F16" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B17">
         <v>38706</v>
@@ -9727,18 +10677,18 @@
         <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E17" t="s">
         <v>178</v>
       </c>
       <c r="F17" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B18">
         <v>38707</v>
@@ -9747,18 +10697,18 @@
         <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E18" t="s">
         <v>178</v>
       </c>
       <c r="F18" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B19">
         <v>38708</v>
@@ -9767,18 +10717,18 @@
         <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
         <v>178</v>
       </c>
       <c r="F19" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B20">
         <v>38709</v>
@@ -9787,18 +10737,18 @@
         <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F20" t="s">
-        <v>280</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s">
         <v>136</v>
@@ -9807,13 +10757,293 @@
         <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E21" t="s">
         <v>178</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>369</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" t="s">
+        <v>370</v>
+      </c>
+      <c r="E22" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>372</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C23" t="s">
+        <v>324</v>
+      </c>
+      <c r="D23" t="s">
+        <v>373</v>
+      </c>
+      <c r="E23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C24" t="s">
+        <v>324</v>
+      </c>
+      <c r="D24" t="s">
+        <v>376</v>
+      </c>
+      <c r="E24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>378</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25" t="s">
+        <v>324</v>
+      </c>
+      <c r="D25" t="s">
+        <v>379</v>
+      </c>
+      <c r="E25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F25" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>381</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C26" t="s">
+        <v>324</v>
+      </c>
+      <c r="D26" t="s">
+        <v>382</v>
+      </c>
+      <c r="E26" t="s">
+        <v>276</v>
+      </c>
+      <c r="F26" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>389</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C27" t="s">
+        <v>324</v>
+      </c>
+      <c r="D27" t="s">
+        <v>390</v>
+      </c>
+      <c r="E27" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>405</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>406</v>
+      </c>
+      <c r="E28" t="s">
+        <v>178</v>
+      </c>
+      <c r="F28" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>411</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C29" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" t="s">
+        <v>412</v>
+      </c>
+      <c r="E29" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" t="s">
+        <v>324</v>
+      </c>
+      <c r="D30" t="s">
+        <v>418</v>
+      </c>
+      <c r="E30" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>423</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C31" t="s">
+        <v>324</v>
+      </c>
+      <c r="D31" t="s">
+        <v>424</v>
+      </c>
+      <c r="E31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>429</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C32" t="s">
+        <v>324</v>
+      </c>
+      <c r="D32" t="s">
+        <v>430</v>
+      </c>
+      <c r="E32" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>435</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" t="s">
+        <v>324</v>
+      </c>
+      <c r="D33" t="s">
+        <v>436</v>
+      </c>
+      <c r="E33" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>441</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C34" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E34" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>447</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C35" t="s">
+        <v>324</v>
+      </c>
+      <c r="D35" t="s">
+        <v>448</v>
+      </c>
+      <c r="E35" t="s">
+        <v>178</v>
+      </c>
+      <c r="F35" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/control/Control_Ejecucion.xlsx
+++ b/control/Control_Ejecucion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GreenSQA\AppData\Local\Temp\claude\c--ATM-AppMovil-MiBanco\4bd799e8-9fec-418b-87c7-f5e93e1a90ec\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GreenSQA\AppData\Local\Temp\claude\c--ATM-AppMovil-MiBanco\50740a1c-6924-4a95-a41b-7812b3fa8b07\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4F6607-86F2-4A1B-AA58-74CED9A8F86B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB79AECE-8794-4127-B6FC-B443C832361B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="395">
   <si>
     <t>Caso</t>
   </si>
@@ -55,9 +55,6 @@
     <t>38498 - Registro exitoso con CC</t>
   </si>
   <si>
-    <t>REG-001</t>
-  </si>
-  <si>
     <t>CC</t>
   </si>
   <si>
@@ -65,18 +62,6 @@
   </si>
   <si>
     <t>Registro 1 de 3 - cliente del listado, clave generada</t>
-  </si>
-  <si>
-    <t>REG-002</t>
-  </si>
-  <si>
-    <t>Registro 2 de 3 - cliente del listado, clave generada</t>
-  </si>
-  <si>
-    <t>REG-003</t>
-  </si>
-  <si>
-    <t>Registro 3 de 3 - cliente del listado, clave generada</t>
   </si>
   <si>
     <t>ID Azure</t>
@@ -796,9 +781,6 @@
     <t>Lista desplegable con los casos ya construidos (Id Azure - nombre). Solo se ejecutan casos de la lista.</t>
   </si>
   <si>
-    <t>Identificador unico de la iteracion (ej. REG-001). Nombra la carpeta de evidencias y aparece en el reporte. No puede repetirse entre filas con Ejecutar = SI.</t>
-  </si>
-  <si>
     <t>SI = se ejecuta. NO o vacio = se omite.</t>
   </si>
   <si>
@@ -814,9 +796,6 @@
     <t>4. Motor de reglas</t>
   </si>
   <si>
-    <t>Antes de ejecutar valida cada fila con Ejecutar = SI: que el caso exista, que IdPrueba sea unico y que los datos obligatorios del caso esten completos y con formato valido. Una fila que no cumple no se ejecuta: queda NO_EJECUTADA con el motivo, en el reporte y en el control de resultados.</t>
-  </si>
-  <si>
     <t>RN-R07</t>
   </si>
   <si>
@@ -910,15 +889,9 @@
     <t>@38519</t>
   </si>
   <si>
-    <t>LOG-001</t>
-  </si>
-  <si>
     <t>Login con cliente registrado del listado</t>
   </si>
   <si>
-    <t>REG-SMS-001</t>
-  </si>
-  <si>
     <t>Pendiente: clientes con la linea de prueba sin registrar (solicitados)</t>
   </si>
   <si>
@@ -940,9 +913,6 @@
     <t>Variante CE de 38499 (mismo escenario). AUTO toma un CE DISPONIBLE con LINEA_SMS = SI. Ejecutar en el dispositivo fisico con la SIM de esa linea. Clientes escasos: un solo intento por cliente.</t>
   </si>
   <si>
-    <t>REG-SMS-CE-001</t>
-  </si>
-  <si>
     <t>CE</t>
   </si>
   <si>
@@ -970,9 +940,6 @@
     <t>Como 38519: AUTO o vacio toma un cliente REGISTRADO con clave del listado (sin LINEA_SMS); no lo consume. Si es el primer ingreso del cliente, cierra sesion y vuelve a ingresar para que aparezca 'Ultimo ingreso'. Cierra sesion al terminar.</t>
   </si>
   <si>
-    <t>HOME-001</t>
-  </si>
-  <si>
     <t>Ultimo ingreso en el encabezado del Home</t>
   </si>
   <si>
@@ -988,9 +955,6 @@
     <t>Variante CE de 38519 (mismo escenario). AUTO o vacio toma un CE REGISTRADO con clave del listado (prefiere los que no tienen LINEA_SMS); no lo consume. Cierra sesion al terminar.</t>
   </si>
   <si>
-    <t>LOG-CE-001</t>
-  </si>
-  <si>
     <t>Login con CE registrado del listado</t>
   </si>
   <si>
@@ -1006,9 +970,6 @@
     <t>Variante CE de 38498 (mismo escenario). AUTO toma un CE DISPONIBLE sin LINEA_SMS (los de la linea se reservan para 38503). Hoy no hay CE disponibles sin linea: solicitar datos.</t>
   </si>
   <si>
-    <t>REG-CE-001</t>
-  </si>
-  <si>
     <t>Pendiente: no hay clientes CE disponibles sin la linea de prueba</t>
   </si>
   <si>
@@ -1024,9 +985,6 @@
     <t>AUTO o vacio toma un cliente REGISTRADO con clave del listado; no lo consume. Cierra sesion al terminar.</t>
   </si>
   <si>
-    <t>HOME-002</t>
-  </si>
-  <si>
     <t>Saludo y pregunta del Home</t>
   </si>
   <si>
@@ -1039,9 +997,6 @@
     <t>@38703</t>
   </si>
   <si>
-    <t>HOME-ACC-001</t>
-  </si>
-  <si>
     <t>Acceso Bre-B (parte superior)</t>
   </si>
   <si>
@@ -1054,9 +1009,6 @@
     <t>@38704</t>
   </si>
   <si>
-    <t>HOME-ACC-002</t>
-  </si>
-  <si>
     <t>Acceso Pedir Credito (parte superior)</t>
   </si>
   <si>
@@ -1069,9 +1021,6 @@
     <t>@38711</t>
   </si>
   <si>
-    <t>HOME-MENU-001</t>
-  </si>
-  <si>
     <t>Menu inferior: 5 accesos en orden</t>
   </si>
   <si>
@@ -1081,18 +1030,12 @@
     <t>38529 - Recuperacion de clave con CC</t>
   </si>
   <si>
-    <t>REC-001</t>
-  </si>
-  <si>
     <t>Recuperacion de clave: cambia la clave de un cliente registrado del listado</t>
   </si>
   <si>
     <t>38526 - OTP en la recuperacion de clave</t>
   </si>
   <si>
-    <t>REC-OTP-001</t>
-  </si>
-  <si>
     <t>OTP en la recuperacion de clave (mismo escenario de 38529)</t>
   </si>
   <si>
@@ -1156,9 +1099,6 @@
     <t>@38706</t>
   </si>
   <si>
-    <t>Como 38705 con CORRIENTE. Hoy ningun cliente revisado tiene cuenta corriente: solicitar datos o informar el documento.</t>
-  </si>
-  <si>
     <t>38707 - Producto credito de libre inversion (Prestamos) en el Home</t>
   </si>
   <si>
@@ -1186,36 +1126,15 @@
     <t>TipoDocumento (CC), TipoProducto, Monto</t>
   </si>
   <si>
-    <t>PROD-AHO-001</t>
-  </si>
-  <si>
     <t>Cuenta de ahorro en el Home</t>
   </si>
   <si>
-    <t>PROD-PRE-001</t>
-  </si>
-  <si>
-    <t>Prestamos (libre inversion) en el Home</t>
-  </si>
-  <si>
-    <t>PROD-ROT-001</t>
-  </si>
-  <si>
     <t>Credito rotativo en el Home</t>
   </si>
   <si>
-    <t>PROD-PRA-001</t>
-  </si>
-  <si>
     <t>Banner de credito pre-aprobado</t>
   </si>
   <si>
-    <t>PROD-COR-001</t>
-  </si>
-  <si>
-    <t>SALDO-001</t>
-  </si>
-  <si>
     <t>Solo casos de productos del Home (38702, 38705 a 38709). Lista: AHORRO, CORRIENTE, PRESTAMO (en la app se llama Prestamos; el caso 38707 lo llama libre inversion), ROTATIVO, PRE_APROBADO. Vacio = el producto del caso; en 38709 es obligatorio (producto cuyo saldo se compara). Con NumDocumento AUTO se busca en el listado un cliente REGISTRADO que muestre el producto (columna PRODUCTOS_HOME), revisando hasta 3 clientes. Dejar vacia en los demas casos.</t>
   </si>
   <si>
@@ -1249,79 +1168,16 @@
     <t>Como 38519: AUTO toma un cliente REGISTRADO con clave. Al ingresar valida que Tus cuentas y Tus creditos muestren el indicador de carga (Cargando..., skeleton) antes de los saldos y que luego aparezcan los montos. Captura del skeleton como evidencia. Si el backend responde muy rapido el skeleton puede no alcanzar a verse y la fila falla con ese detalle. Cierra sesion al terminar.</t>
   </si>
   <si>
-    <t>SKEL-001</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>43110437.46</t>
-  </si>
-  <si>
-    <t>SALDO-002</t>
-  </si>
-  <si>
-    <t>43110438.46</t>
-  </si>
-  <si>
     <t>Disponible en la hoja Control (SKEL-001)</t>
   </si>
   <si>
-    <t>Pendiente: ningun cliente registrado muestra cuenta corriente (verificado 12/10); informar un documento con el producto</t>
-  </si>
-  <si>
-    <t>Verificado 12/10 con monto tomado de la app (no del backend). Pendiente: Monto esperado segun el backend</t>
-  </si>
-  <si>
-    <t>Verificacion tecnica 12/10: monto alterado en 1 peso falla como se espera. Eliminar o reutilizar con montos del backend</t>
-  </si>
-  <si>
     <t>Skeleton (Cargando...) mientras el Home obtiene los saldos; se observa por DevTools del WebView</t>
   </si>
   <si>
-    <t>LOG-002</t>
-  </si>
-  <si>
-    <t>REG-004</t>
-  </si>
-  <si>
-    <t>REG-005</t>
-  </si>
-  <si>
     <t>Clave de 4 digitos. Con NumDocumento AUTO: dejar vacia (registro y recuperacion generan una valida segun RN-R07; login y Home usan la clave guardada en el listado). Con un numero de documento informado la Clave es OBLIGATORIA: la que se crea en el registro, la actual del cliente en login/Home/productos o la nueva en la recuperacion; si falta, la fila queda NO EJECUTADA. En registro y recuperacion debe cumplir RN-R07.</t>
-  </si>
-  <si>
-    <t>LOG-005</t>
-  </si>
-  <si>
-    <t>SALU-PREG-002</t>
-  </si>
-  <si>
-    <t>HOME-ACC-003</t>
-  </si>
-  <si>
-    <t>PROD-PRA-002</t>
-  </si>
-  <si>
-    <t>MENU-INF-001</t>
-  </si>
-  <si>
-    <t>PROD-ROT-002</t>
-  </si>
-  <si>
-    <t>PROD-LIB-002</t>
-  </si>
-  <si>
-    <t>PROD-CORR-002</t>
-  </si>
-  <si>
-    <t>PROD-AHO-002</t>
-  </si>
-  <si>
-    <t>HOME-ACC-004</t>
-  </si>
-  <si>
-    <t>2658679.07</t>
   </si>
   <si>
     <t>39561</t>
@@ -1562,9 +1418,6 @@
     <t>@39562</t>
   </si>
   <si>
-    <t>Mismo escenario y reglas de 38706 (repite su texto). Como 38705 con CORRIENTE. Hoy ningun cliente revisado tiene cuenta corriente: solicitar datos o informar el documento.</t>
-  </si>
-  <si>
     <t>39563 - Producto credito de libre inversion (Prestamos) en el Home (Cuentas)</t>
   </si>
   <si>
@@ -1619,39 +1472,12 @@
     <t>Disponible en la hoja Control (CTA-DET-001). Movimientos: acepta la lista o el aviso sin movimientos (ningun cliente de prueba tiene movimientos al 15/10)</t>
   </si>
   <si>
-    <t>CTA-DET-001</t>
-  </si>
-  <si>
-    <t>Detalle de la cuenta de ahorros</t>
-  </si>
-  <si>
-    <t>SALDO-003</t>
-  </si>
-  <si>
-    <t>REC-OTP-002</t>
-  </si>
-  <si>
-    <t>SKEL-002</t>
-  </si>
-  <si>
-    <t>HOME-003</t>
-  </si>
-  <si>
-    <t>CTA-AHO-001</t>
-  </si>
-  <si>
     <t>Cuenta de ahorro en el Home (repite 38705)</t>
   </si>
   <si>
-    <t>CTA-PRE-001</t>
-  </si>
-  <si>
     <t>Prestamos en el Home (repite 38707)</t>
   </si>
   <si>
-    <t>CTA-ROT-001</t>
-  </si>
-  <si>
     <t>Credito rotativo en el Home (repite 38708)</t>
   </si>
   <si>
@@ -1667,9 +1493,6 @@
     <t>Disponible en la hoja Control (HOME-BAN-001). Con una sola campana, el deslizamiento queda como observacion</t>
   </si>
   <si>
-    <t>HOME-BAN-001</t>
-  </si>
-  <si>
     <t>Banner Exclusivo para ti</t>
   </si>
   <si>
@@ -1685,12 +1508,12 @@
     <t>Disponible en la hoja Control (CTA-TRX-001). Requiere un cliente con movimientos. Sin cuenta de origen ni destino en la app: observacion</t>
   </si>
   <si>
-    <t>CTA-TRX-001</t>
-  </si>
-  <si>
     <t>Detalle de una transaccion (requiere cliente con movimientos)</t>
   </si>
   <si>
+    <t>Detalle de cuenta con movimientos (cliente del equipo funcional)</t>
+  </si>
+  <si>
     <t>39572 - Descargar comprobante de una transaccion</t>
   </si>
   <si>
@@ -1703,9 +1526,6 @@
     <t>Disponible en la hoja Control (CTA-DES-001). Requiere un cliente con movimientos. La imagen se adjunta a la evidencia y se borra del dispositivo</t>
   </si>
   <si>
-    <t>CTA-DES-001</t>
-  </si>
-  <si>
     <t>Descargar comprobante (requiere cliente con movimientos)</t>
   </si>
   <si>
@@ -1721,9 +1541,6 @@
     <t>Disponible en la hoja Control (CTA-COM-001). Requiere un cliente con movimientos. El envio por una app externa queda manual</t>
   </si>
   <si>
-    <t>CTA-COM-001</t>
-  </si>
-  <si>
     <t>Compartir comprobante (requiere cliente con movimientos)</t>
   </si>
   <si>
@@ -1739,9 +1556,6 @@
     <t>Disponible en la hoja Control (CTA-MOV-001). Mismo escenario que 39569 y 39570. Con menos de 20 movimientos el corte en 20 queda como observacion</t>
   </si>
   <si>
-    <t>CTA-MOV-001</t>
-  </si>
-  <si>
     <t>Movimientos: maximo 20, orden y sin paginacion</t>
   </si>
   <si>
@@ -1757,9 +1571,6 @@
     <t>Disponible en la hoja Control (CTA-MOV-002). Mismo escenario de 39567; se valida en el detalle de cuenta (pendiente confirmar el titulo)</t>
   </si>
   <si>
-    <t>CTA-MOV-002</t>
-  </si>
-  <si>
     <t>Sin Ver mas (mismo escenario de 39567)</t>
   </si>
   <si>
@@ -1775,9 +1586,6 @@
     <t>Disponible en la hoja Control (CTA-MOV-003). Mismo escenario de 39567; la ausencia de peticiones de red queda manual</t>
   </si>
   <si>
-    <t>CTA-MOV-003</t>
-  </si>
-  <si>
     <t>Sin paginacion (mismo escenario de 39567)</t>
   </si>
   <si>
@@ -1793,17 +1601,35 @@
     <t>Disponible en la hoja Control (CTA-MOV-004). La exclusion de movimientos mas antiguos requiere un cliente que los tenga</t>
   </si>
   <si>
-    <t>CTA-MOV-004</t>
-  </si>
-  <si>
-    <t>Movimientos del ultimo mes</t>
+    <t>Cliente con 85 transacciones (30 en abril 2026): la app solo muestra las del ultimo mes</t>
+  </si>
+  <si>
+    <t>Cliente con cuenta corriente entregado por el equipo funcional (20/10)</t>
+  </si>
+  <si>
+    <t>Antes de ejecutar valida cada fila con Ejecutar = SI: que el caso exista, que IdPrueba no se repita (el generado nunca se repite) y que los datos obligatorios del caso esten completos y con formato valido. Una fila que no cumple no se ejecuta: queda NO_EJECUTADA con el motivo, en el reporte y en el control de resultados.</t>
+  </si>
+  <si>
+    <t>Como 38705 con CORRIENTE. Los clientes del listado no tienen cuenta corriente: informe NumDocumento y Clave del cliente entregado por el equipo funcional (20/10). La app muestra Cuentas corrientes **** 1234.</t>
+  </si>
+  <si>
+    <t>Mismo escenario y reglas de 38706 (repite su texto). Como 38705 con CORRIENTE. Los clientes del listado no tienen cuenta corriente: informe NumDocumento y Clave del cliente entregado por el equipo funcional (20/10). La app muestra Cuentas corrientes **** 1234.</t>
+  </si>
+  <si>
+    <t>Prestamos (libre inversion) en el Home</t>
+  </si>
+  <si>
+    <t>Si no tiene uno, dejela vacia: se genera con el prefijo del caso y un consecutivo (ej. REG-CC-001, PROD-AHORRO-002, CTA-MOV20-001). Si tiene uno, escribalo y se usa ese (no puede repetirse entre filas con Ejecutar = SI). Nombra la carpeta de evidencias y aparece en el reporte y en Control_Resultado.xlsx.</t>
+  </si>
+  <si>
+    <t>Informe TipoProducto y el Monto esperado del producto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1827,13 +1653,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1891,7 +1710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1920,7 +1739,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2226,7 +2044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J500"/>
+  <dimension ref="A1:J477"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2262,10 +2080,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -2275,836 +2093,776 @@
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>185</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>211</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>187</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>271</v>
+      </c>
       <c r="J10" s="2" t="s">
-        <v>218</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>223</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>238</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>242</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>245</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>277</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>278</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>279</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>280</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>281</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>283</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>284</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>285</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>299</v>
-      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>286</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>300</v>
-      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>305</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>298</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>299</v>
-      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>395</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>302</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="I24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>306</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>309</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>308</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="J26" s="2" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>310</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>312</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>396</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>397</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>313</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>398</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>315</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>314</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>321</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -3112,21 +2870,11 @@
       <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -3134,21 +2882,11 @@
       <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -3156,21 +2894,11 @@
       <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -3178,47 +2906,23 @@
       <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>322</v>
-      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -3226,292 +2930,148 @@
       <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="2" t="s">
-        <v>394</v>
-      </c>
+      <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="2" t="s">
-        <v>400</v>
-      </c>
+      <c r="J43" s="2"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="2" t="s">
-        <v>402</v>
-      </c>
+      <c r="J44" s="2"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="2" t="s">
-        <v>404</v>
-      </c>
+      <c r="J45" s="2"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="2" t="s">
-        <v>410</v>
-      </c>
+      <c r="J46" s="2"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="2" t="s">
-        <v>416</v>
-      </c>
+      <c r="J47" s="2"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="2" t="s">
-        <v>422</v>
-      </c>
+      <c r="J48" s="2"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="2" t="s">
-        <v>428</v>
-      </c>
+      <c r="J49" s="2"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
-      <c r="J50" s="2" t="s">
-        <v>434</v>
-      </c>
+      <c r="J50" s="2"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="2" t="s">
-        <v>440</v>
-      </c>
+      <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="2" t="s">
-        <v>446</v>
-      </c>
+      <c r="J52" s="2"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="2" t="s">
-        <v>452</v>
-      </c>
+      <c r="J53" s="2"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
@@ -8601,288 +8161,15 @@
       <c r="I477" s="2"/>
       <c r="J477" s="2"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A478" s="2"/>
-      <c r="B478" s="2"/>
-      <c r="C478" s="2"/>
-      <c r="D478" s="2"/>
-      <c r="E478" s="2"/>
-      <c r="F478" s="2"/>
-      <c r="G478" s="2"/>
-      <c r="H478" s="2"/>
-      <c r="I478" s="2"/>
-      <c r="J478" s="2"/>
-    </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A479" s="2"/>
-      <c r="B479" s="2"/>
-      <c r="C479" s="2"/>
-      <c r="D479" s="2"/>
-      <c r="E479" s="2"/>
-      <c r="F479" s="2"/>
-      <c r="G479" s="2"/>
-      <c r="H479" s="2"/>
-      <c r="I479" s="2"/>
-      <c r="J479" s="2"/>
-    </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A480" s="2"/>
-      <c r="B480" s="2"/>
-      <c r="C480" s="2"/>
-      <c r="D480" s="2"/>
-      <c r="E480" s="2"/>
-      <c r="F480" s="2"/>
-      <c r="G480" s="2"/>
-      <c r="H480" s="2"/>
-      <c r="I480" s="2"/>
-      <c r="J480" s="2"/>
-    </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A481" s="2"/>
-      <c r="B481" s="2"/>
-      <c r="C481" s="2"/>
-      <c r="D481" s="2"/>
-      <c r="E481" s="2"/>
-      <c r="F481" s="2"/>
-      <c r="G481" s="2"/>
-      <c r="H481" s="2"/>
-      <c r="I481" s="2"/>
-      <c r="J481" s="2"/>
-    </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A482" s="2"/>
-      <c r="B482" s="2"/>
-      <c r="C482" s="2"/>
-      <c r="D482" s="2"/>
-      <c r="E482" s="2"/>
-      <c r="F482" s="2"/>
-      <c r="G482" s="2"/>
-      <c r="H482" s="2"/>
-      <c r="I482" s="2"/>
-      <c r="J482" s="2"/>
-    </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A483" s="2"/>
-      <c r="B483" s="2"/>
-      <c r="C483" s="2"/>
-      <c r="D483" s="2"/>
-      <c r="E483" s="2"/>
-      <c r="F483" s="2"/>
-      <c r="G483" s="2"/>
-      <c r="H483" s="2"/>
-      <c r="I483" s="2"/>
-      <c r="J483" s="2"/>
-    </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A484" s="2"/>
-      <c r="B484" s="2"/>
-      <c r="C484" s="2"/>
-      <c r="D484" s="2"/>
-      <c r="E484" s="2"/>
-      <c r="F484" s="2"/>
-      <c r="G484" s="2"/>
-      <c r="H484" s="2"/>
-      <c r="I484" s="2"/>
-      <c r="J484" s="2"/>
-    </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A485" s="2"/>
-      <c r="B485" s="2"/>
-      <c r="C485" s="2"/>
-      <c r="D485" s="2"/>
-      <c r="E485" s="2"/>
-      <c r="F485" s="2"/>
-      <c r="G485" s="2"/>
-      <c r="H485" s="2"/>
-      <c r="I485" s="2"/>
-      <c r="J485" s="2"/>
-    </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A486" s="2"/>
-      <c r="B486" s="2"/>
-      <c r="C486" s="2"/>
-      <c r="D486" s="2"/>
-      <c r="E486" s="2"/>
-      <c r="F486" s="2"/>
-      <c r="G486" s="2"/>
-      <c r="H486" s="2"/>
-      <c r="I486" s="2"/>
-      <c r="J486" s="2"/>
-    </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A487" s="2"/>
-      <c r="B487" s="2"/>
-      <c r="C487" s="2"/>
-      <c r="D487" s="2"/>
-      <c r="E487" s="2"/>
-      <c r="F487" s="2"/>
-      <c r="G487" s="2"/>
-      <c r="H487" s="2"/>
-      <c r="I487" s="2"/>
-      <c r="J487" s="2"/>
-    </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A488" s="2"/>
-      <c r="B488" s="2"/>
-      <c r="C488" s="2"/>
-      <c r="D488" s="2"/>
-      <c r="E488" s="2"/>
-      <c r="F488" s="2"/>
-      <c r="G488" s="2"/>
-      <c r="H488" s="2"/>
-      <c r="I488" s="2"/>
-      <c r="J488" s="2"/>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A489" s="2"/>
-      <c r="B489" s="2"/>
-      <c r="C489" s="2"/>
-      <c r="D489" s="2"/>
-      <c r="E489" s="2"/>
-      <c r="F489" s="2"/>
-      <c r="G489" s="2"/>
-      <c r="H489" s="2"/>
-      <c r="I489" s="2"/>
-      <c r="J489" s="2"/>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A490" s="2"/>
-      <c r="B490" s="2"/>
-      <c r="C490" s="2"/>
-      <c r="D490" s="2"/>
-      <c r="E490" s="2"/>
-      <c r="F490" s="2"/>
-      <c r="G490" s="2"/>
-      <c r="H490" s="2"/>
-      <c r="I490" s="2"/>
-      <c r="J490" s="2"/>
-    </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A491" s="2"/>
-      <c r="B491" s="2"/>
-      <c r="C491" s="2"/>
-      <c r="D491" s="2"/>
-      <c r="E491" s="2"/>
-      <c r="F491" s="2"/>
-      <c r="G491" s="2"/>
-      <c r="H491" s="2"/>
-      <c r="I491" s="2"/>
-      <c r="J491" s="2"/>
-    </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A492" s="2"/>
-      <c r="B492" s="2"/>
-      <c r="C492" s="2"/>
-      <c r="D492" s="2"/>
-      <c r="E492" s="2"/>
-      <c r="F492" s="2"/>
-      <c r="G492" s="2"/>
-      <c r="H492" s="2"/>
-      <c r="I492" s="2"/>
-      <c r="J492" s="2"/>
-    </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A493" s="2"/>
-      <c r="B493" s="2"/>
-      <c r="C493" s="2"/>
-      <c r="D493" s="2"/>
-      <c r="E493" s="2"/>
-      <c r="F493" s="2"/>
-      <c r="G493" s="2"/>
-      <c r="H493" s="2"/>
-      <c r="I493" s="2"/>
-      <c r="J493" s="2"/>
-    </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A494" s="2"/>
-      <c r="B494" s="2"/>
-      <c r="C494" s="2"/>
-      <c r="D494" s="2"/>
-      <c r="E494" s="2"/>
-      <c r="F494" s="2"/>
-      <c r="G494" s="2"/>
-      <c r="H494" s="2"/>
-      <c r="I494" s="2"/>
-      <c r="J494" s="2"/>
-    </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A495" s="2"/>
-      <c r="B495" s="2"/>
-      <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
-      <c r="E495" s="2"/>
-      <c r="F495" s="2"/>
-      <c r="G495" s="2"/>
-      <c r="H495" s="2"/>
-      <c r="I495" s="2"/>
-      <c r="J495" s="2"/>
-    </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A496" s="2"/>
-      <c r="B496" s="2"/>
-      <c r="C496" s="2"/>
-      <c r="D496" s="2"/>
-      <c r="E496" s="2"/>
-      <c r="F496" s="2"/>
-      <c r="G496" s="2"/>
-      <c r="H496" s="2"/>
-      <c r="I496" s="2"/>
-      <c r="J496" s="2"/>
-    </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A497" s="2"/>
-      <c r="B497" s="2"/>
-      <c r="C497" s="2"/>
-      <c r="D497" s="2"/>
-      <c r="E497" s="2"/>
-      <c r="F497" s="2"/>
-      <c r="G497" s="2"/>
-      <c r="H497" s="2"/>
-      <c r="I497" s="2"/>
-      <c r="J497" s="2"/>
-    </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A498" s="2"/>
-      <c r="B498" s="2"/>
-      <c r="C498" s="2"/>
-      <c r="D498" s="2"/>
-      <c r="E498" s="2"/>
-      <c r="F498" s="2"/>
-      <c r="G498" s="2"/>
-      <c r="H498" s="2"/>
-      <c r="I498" s="2"/>
-      <c r="J498" s="2"/>
-    </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A499" s="2"/>
-      <c r="B499" s="2"/>
-      <c r="C499" s="2"/>
-      <c r="D499" s="2"/>
-      <c r="E499" s="2"/>
-      <c r="F499" s="2"/>
-      <c r="G499" s="2"/>
-      <c r="H499" s="2"/>
-      <c r="I499" s="2"/>
-      <c r="J499" s="2"/>
-    </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A500" s="2"/>
-      <c r="B500" s="2"/>
-      <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
-      <c r="E500" s="2"/>
-      <c r="F500" s="2"/>
-      <c r="G500" s="2"/>
-      <c r="H500" s="2"/>
-      <c r="I500" s="2"/>
-      <c r="J500" s="2"/>
-    </row>
   </sheetData>
+  <sortState ref="A2:J35">
+    <sortCondition ref="A2"/>
+  </sortState>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C500" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C477" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D500" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D477" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"CC,CE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8895,13 +8182,13 @@
           <x14:formula1>
             <xm:f>Catalogo!$H$2:$H$6</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H500</xm:sqref>
+          <xm:sqref>H2:H477</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{ADF90D24-994E-4A2F-A10B-81ED9C0DAF51}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Caso no valido" error="Seleccione un caso de la lista (casos construidos)." xr:uid="{6FB47969-1A9F-49CB-9F65-56E46E498E2B}">
           <x14:formula1>
             <xm:f>Catalogo!$A$2:$A$35</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A500</xm:sqref>
+          <xm:sqref>A2:A477</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8928,1148 +8215,1148 @@
   <sheetData>
     <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="406" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="406" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="406" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="232" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="174" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="232" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="203" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="174" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="116" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>408</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
-        <v>323</v>
+      <c r="A27" s="12" t="s">
+        <v>275</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="203" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
-        <v>327</v>
+      <c r="A28" s="12" t="s">
+        <v>279</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="174" x14ac:dyDescent="0.35">
-      <c r="A29" s="13" t="s">
-        <v>329</v>
+      <c r="A29" s="12" t="s">
+        <v>281</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>386</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>331</v>
+      <c r="A30" s="12" t="s">
+        <v>283</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
-        <v>332</v>
+      <c r="A31" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="290" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
-        <v>333</v>
+      <c r="A32" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="203" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
-        <v>337</v>
+      <c r="A33" s="12" t="s">
+        <v>289</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>432</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
-        <v>341</v>
+      <c r="A34" s="12" t="s">
+        <v>293</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>450</v>
+        <v>386</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="145" x14ac:dyDescent="0.35">
-      <c r="A35" s="13" t="s">
-        <v>345</v>
+      <c r="A35" s="12" t="s">
+        <v>297</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>438</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
-        <v>349</v>
+      <c r="A36" s="12" t="s">
+        <v>301</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>444</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="116" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
-        <v>353</v>
+      <c r="A37" s="12" t="s">
+        <v>305</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>414</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="116" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
-        <v>357</v>
+      <c r="A38" s="12" t="s">
+        <v>309</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>358</v>
+        <v>310</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>420</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="13" t="s">
-        <v>361</v>
+      <c r="A39" s="12" t="s">
+        <v>313</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>363</v>
+        <v>315</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -10089,7 +9376,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -10098,18 +9385,18 @@
     </row>
     <row r="3" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -10118,7 +9405,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B6" s="10"/>
     </row>
@@ -10127,15 +9414,15 @@
         <v>0</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>147</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -10143,7 +9430,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -10151,7 +9438,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
@@ -10159,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
@@ -10167,7 +9454,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -10175,23 +9462,23 @@
         <v>6</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -10199,7 +9486,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -10208,18 +9495,18 @@
     </row>
     <row r="18" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>153</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -10228,10 +9515,10 @@
     </row>
     <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -10240,42 +9527,42 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -10284,18 +9571,18 @@
     </row>
     <row r="29" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -10304,18 +9591,18 @@
     </row>
     <row r="32" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -10333,22 +9620,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H1" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -10356,694 +9643,694 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F2" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="H2" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H3" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="H4" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="H5" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F6" t="s">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="H6" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F7" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F8" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F9" t="s">
-        <v>367</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="B10">
         <v>38698</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="E10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F10" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="E11" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F11" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F12" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B13">
         <v>38702</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F13" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F14" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="E15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F15" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="B16">
         <v>38705</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F16" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="B17">
         <v>38706</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="E17" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>267</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="B18">
         <v>38707</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="B19">
         <v>38708</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="E19" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F19" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="B20">
         <v>38709</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="E20" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="F20" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F21" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C22" t="s">
+        <v>276</v>
+      </c>
+      <c r="D22" t="s">
+        <v>322</v>
+      </c>
+      <c r="E22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22" t="s">
         <v>323</v>
-      </c>
-      <c r="C22" t="s">
-        <v>324</v>
-      </c>
-      <c r="D22" t="s">
-        <v>370</v>
-      </c>
-      <c r="E22" t="s">
-        <v>178</v>
-      </c>
-      <c r="F22" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="C23" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D23" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
       <c r="E23" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F23" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>326</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="C24" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D24" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="E24" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F24" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>378</v>
+        <v>329</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C25" t="s">
+        <v>276</v>
+      </c>
+      <c r="D25" t="s">
+        <v>330</v>
+      </c>
+      <c r="E25" t="s">
+        <v>171</v>
+      </c>
+      <c r="F25" t="s">
         <v>331</v>
-      </c>
-      <c r="C25" t="s">
-        <v>324</v>
-      </c>
-      <c r="D25" t="s">
-        <v>379</v>
-      </c>
-      <c r="E25" t="s">
-        <v>178</v>
-      </c>
-      <c r="F25" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D26" t="s">
-        <v>382</v>
+        <v>333</v>
       </c>
       <c r="E26" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="F26" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D27" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
       <c r="E27" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="E28" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F28" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>411</v>
+        <v>352</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29" t="s">
+        <v>276</v>
+      </c>
+      <c r="D29" t="s">
         <v>353</v>
       </c>
-      <c r="C29" t="s">
-        <v>324</v>
-      </c>
-      <c r="D29" t="s">
-        <v>412</v>
-      </c>
       <c r="E29" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F29" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="C30" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D30" t="s">
-        <v>418</v>
+        <v>359</v>
       </c>
       <c r="E30" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F30" t="s">
-        <v>419</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="C31" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D31" t="s">
-        <v>424</v>
+        <v>364</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s">
-        <v>425</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>429</v>
+        <v>368</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="C32" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D32" t="s">
-        <v>430</v>
+        <v>369</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>431</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="C33" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D33" t="s">
-        <v>436</v>
+        <v>374</v>
       </c>
       <c r="E33" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F33" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>441</v>
+        <v>378</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D34" t="s">
-        <v>442</v>
+        <v>379</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F34" t="s">
-        <v>443</v>
+        <v>380</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>447</v>
+        <v>383</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C35" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="D35" t="s">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="E35" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F35" t="s">
-        <v>449</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
